--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BE6B42-9523-4AA0-A17A-023514E5030D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0E0E44-26EA-4B0E-8D40-C0AE2F686E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="130" yWindow="420" windowWidth="22730" windowHeight="13380" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -25,6 +25,9 @@
     <sheet name="12," sheetId="161" r:id="rId15"/>
     <sheet name="13" sheetId="157" r:id="rId16"/>
     <sheet name="14" sheetId="162" r:id="rId17"/>
+    <sheet name="15" sheetId="163" r:id="rId18"/>
+    <sheet name="15ауысым" sheetId="164" r:id="rId19"/>
+    <sheet name="16" sheetId="165" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,8 +50,50 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{BCE33F81-433F-4BA6-A96D-CE836DC0564A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">Автор:
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{A0A37D24-DBCE-44AC-AD3B-CC1277CD5E0F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">Автор:
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3498" uniqueCount="261">
   <si>
     <t>СБ</t>
   </si>
@@ -810,6 +855,45 @@
   <si>
     <t>13-H2685/12н</t>
   </si>
+  <si>
+    <t xml:space="preserve">15.10.2026 ж </t>
+  </si>
+  <si>
+    <t xml:space="preserve">34-Н3407/12 </t>
+  </si>
+  <si>
+    <t>34-Н3400/12</t>
+  </si>
+  <si>
+    <t>51-Н3585/12н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34-Н3164/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">34-Н2797/12 </t>
+  </si>
+  <si>
+    <t>34-Н3391/12 д/н</t>
+  </si>
+  <si>
+    <t>34-Н3404/12 д/н</t>
+  </si>
+  <si>
+    <t>С13-H287712</t>
+  </si>
+  <si>
+    <t>13-H2657/12</t>
+  </si>
+  <si>
+    <t>13-H2809/12</t>
+  </si>
+  <si>
+    <t>36-H3182/12н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.10.2026 ж </t>
+  </si>
 </sst>
 </file>
 
@@ -818,7 +902,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -976,6 +1060,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1413,7 +1505,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="298">
+  <cellXfs count="304">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2204,15 +2296,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2230,6 +2313,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="3" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2530,31 +2640,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F59D383D-7ECB-4240-BBCD-CA0EC74C6B13}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="116"/>
       <c r="B1" s="117"/>
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="288" t="s">
+      <c r="F1" s="301" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="289"/>
+      <c r="G1" s="302"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -2564,7 +2674,7 @@
       <c r="N1" s="115"/>
       <c r="O1" s="115"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="120" t="s">
         <v>0</v>
       </c>
@@ -2603,7 +2713,7 @@
       <c r="N2" s="115"/>
       <c r="O2" s="115"/>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="137" t="s">
         <v>131</v>
       </c>
@@ -2642,7 +2752,7 @@
       <c r="N3" s="115"/>
       <c r="O3" s="115"/>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="129" t="s">
         <v>132</v>
       </c>
@@ -2677,7 +2787,7 @@
       <c r="N4" s="115"/>
       <c r="O4" s="115"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="145"/>
       <c r="B5" s="130" t="s">
         <v>121</v>
@@ -2708,7 +2818,7 @@
       <c r="N5" s="115"/>
       <c r="O5" s="115"/>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="230"/>
       <c r="B6" s="224" t="s">
         <v>129</v>
@@ -2741,7 +2851,7 @@
       <c r="N6" s="115"/>
       <c r="O6" s="115"/>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="155" t="s">
         <v>114</v>
       </c>
@@ -2774,7 +2884,7 @@
       <c r="N7" s="115"/>
       <c r="O7" s="115"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="129" t="s">
         <v>107</v>
       </c>
@@ -2807,7 +2917,7 @@
       <c r="N8" s="115"/>
       <c r="O8" s="115"/>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="137" t="s">
         <v>92</v>
       </c>
@@ -2846,7 +2956,7 @@
       <c r="N9" s="115"/>
       <c r="O9" s="115"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="137" t="s">
         <v>124</v>
       </c>
@@ -2879,7 +2989,7 @@
       <c r="N10" s="115"/>
       <c r="O10" s="115"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="137"/>
       <c r="B11" s="130" t="s">
         <v>108</v>
@@ -2904,7 +3014,7 @@
       <c r="N11" s="115"/>
       <c r="O11" s="115"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="169" t="s">
         <v>113</v>
       </c>
@@ -2931,7 +3041,7 @@
       <c r="N12" s="115"/>
       <c r="O12" s="115"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="137" t="s">
         <v>99</v>
       </c>
@@ -2956,7 +3066,7 @@
       <c r="N13" s="115"/>
       <c r="O13" s="115"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="137" t="s">
         <v>82</v>
       </c>
@@ -2981,7 +3091,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="177"/>
       <c r="B15" s="151"/>
       <c r="C15" s="140"/>
@@ -3000,7 +3110,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="120" t="s">
         <v>37</v>
       </c>
@@ -3037,7 +3147,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="182" t="s">
         <v>44</v>
       </c>
@@ -3070,7 +3180,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="120"/>
       <c r="B18" s="157"/>
       <c r="C18" s="160"/>
@@ -3091,7 +3201,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="185"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -3108,7 +3218,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="120" t="s">
         <v>59</v>
       </c>
@@ -3145,7 +3255,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="195" t="s">
         <v>154</v>
       </c>
@@ -3180,7 +3290,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="195" t="s">
         <v>153</v>
       </c>
@@ -3211,7 +3321,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="228" t="s">
         <v>117</v>
       </c>
@@ -3240,7 +3350,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="229" t="s">
         <v>126</v>
       </c>
@@ -3265,7 +3375,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="201" t="s">
         <v>122</v>
       </c>
@@ -3288,7 +3398,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="201" t="s">
         <v>123</v>
       </c>
@@ -3311,7 +3421,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="192"/>
       <c r="B27" s="205"/>
       <c r="C27" s="206"/>
@@ -3332,7 +3442,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="195"/>
       <c r="B28" s="157"/>
       <c r="C28" s="202"/>
@@ -3353,7 +3463,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="195"/>
       <c r="B29" s="157"/>
       <c r="C29" s="206"/>
@@ -3378,7 +3488,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="211"/>
       <c r="B30" s="157"/>
       <c r="C30" s="202"/>
@@ -3399,7 +3509,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="212"/>
       <c r="B31" s="157"/>
       <c r="C31" s="151"/>
@@ -3420,7 +3530,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="177"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -3439,7 +3549,7 @@
       <c r="N32" s="122"/>
       <c r="O32" s="115"/>
     </row>
-    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="214"/>
       <c r="B33" s="215"/>
       <c r="C33" s="215"/>
@@ -3455,7 +3565,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -3471,7 +3581,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -3487,7 +3597,7 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="115"/>
       <c r="B36" s="115"/>
       <c r="C36" s="115"/>
@@ -3503,7 +3613,7 @@
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="115"/>
       <c r="B37" s="115"/>
       <c r="C37" s="115"/>
@@ -3519,7 +3629,7 @@
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="115"/>
       <c r="B38" s="115"/>
       <c r="C38" s="115"/>
@@ -3535,7 +3645,7 @@
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="115"/>
       <c r="B39" s="115"/>
       <c r="C39" s="115"/>
@@ -3551,7 +3661,7 @@
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="115"/>
       <c r="B40" s="115"/>
       <c r="C40" s="115"/>
@@ -3579,23 +3689,23 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE63104C-AD10-4EE6-9C55-9CDA1F9BE5CA}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="115" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="115" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="223" t="s">
         <v>133</v>
       </c>
@@ -3603,16 +3713,16 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="290" t="s">
+      <c r="F1" s="303" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="290"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
       <c r="K1" s="165"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="121" t="s">
         <v>0</v>
       </c>
@@ -3647,7 +3757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="170" t="s">
         <v>196</v>
       </c>
@@ -3682,7 +3792,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="130" t="s">
         <v>195</v>
       </c>
@@ -3707,7 +3817,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="206"/>
       <c r="B5" s="130" t="s">
         <v>21</v>
@@ -3734,7 +3844,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="130"/>
       <c r="B6" s="130" t="s">
         <v>134</v>
@@ -3763,7 +3873,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="247" t="s">
         <v>114</v>
       </c>
@@ -3792,7 +3902,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="170" t="s">
         <v>194</v>
       </c>
@@ -3821,7 +3931,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="130" t="s">
         <v>92</v>
       </c>
@@ -3857,7 +3967,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="130" t="s">
         <v>222</v>
       </c>
@@ -3888,7 +3998,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="130"/>
       <c r="B11" s="130" t="s">
         <v>137</v>
@@ -3906,7 +4016,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="248" t="s">
         <v>113</v>
       </c>
@@ -3927,7 +4037,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130" t="s">
         <v>99</v>
       </c>
@@ -3947,7 +4057,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="130" t="s">
         <v>82</v>
       </c>
@@ -3973,7 +4083,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="157"/>
       <c r="B15" s="256" t="s">
         <v>219</v>
@@ -3993,7 +4103,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="121" t="s">
         <v>37</v>
       </c>
@@ -4026,7 +4136,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="133" t="s">
         <v>44</v>
       </c>
@@ -4060,7 +4170,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="121"/>
       <c r="B18" s="157"/>
       <c r="C18" s="140"/>
@@ -4079,7 +4189,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="178"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -4095,7 +4205,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="121" t="s">
         <v>59</v>
       </c>
@@ -4131,7 +4241,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="133" t="s">
         <v>154</v>
       </c>
@@ -4159,7 +4269,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="133" t="s">
         <v>153</v>
       </c>
@@ -4191,7 +4301,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="263" t="s">
         <v>224</v>
       </c>
@@ -4216,7 +4326,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="133" t="s">
         <v>223</v>
       </c>
@@ -4241,7 +4351,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="262" t="s">
         <v>122</v>
       </c>
@@ -4267,7 +4377,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="263" t="s">
         <v>123</v>
       </c>
@@ -4288,7 +4398,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="139"/>
       <c r="B27" s="205"/>
       <c r="C27" s="207"/>
@@ -4308,7 +4418,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="251"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -4325,7 +4435,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="251"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -4349,7 +4459,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="166"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -4369,7 +4479,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="205"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -4386,7 +4496,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="157"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -4405,7 +4515,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="165"/>
       <c r="B33" s="165"/>
       <c r="C33" s="165"/>
@@ -4422,7 +4532,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -4439,7 +4549,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -4454,23 +4564,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -4488,23 +4598,23 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5252D90-314A-44E2-B54F-326A5CC5F5C1}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="115" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="115" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="223" t="s">
         <v>133</v>
       </c>
@@ -4512,16 +4622,16 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="290" t="s">
+      <c r="F1" s="303" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="290"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
       <c r="K1" s="165"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="121" t="s">
         <v>0</v>
       </c>
@@ -4556,7 +4666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="130" t="s">
         <v>195</v>
       </c>
@@ -4583,7 +4693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="170" t="s">
         <v>196</v>
       </c>
@@ -4618,7 +4728,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="206"/>
       <c r="B5" s="130" t="s">
         <v>137</v>
@@ -4645,7 +4755,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="130"/>
       <c r="B6" s="130" t="s">
         <v>139</v>
@@ -4674,7 +4784,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="130" t="s">
         <v>99</v>
       </c>
@@ -4697,7 +4807,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="130" t="s">
         <v>82</v>
       </c>
@@ -4722,7 +4832,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="157"/>
       <c r="B9" s="130" t="s">
         <v>106</v>
@@ -4742,7 +4852,7 @@
       <c r="K9" s="130"/>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="247" t="s">
         <v>114</v>
       </c>
@@ -4772,7 +4882,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="170" t="s">
         <v>194</v>
       </c>
@@ -4800,7 +4910,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="130" t="s">
         <v>92</v>
       </c>
@@ -4831,7 +4941,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130" t="s">
         <v>222</v>
       </c>
@@ -4859,7 +4969,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="130"/>
       <c r="B14" s="130" t="s">
         <v>95</v>
@@ -4881,7 +4991,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="248" t="s">
         <v>113</v>
       </c>
@@ -4903,7 +5013,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="121" t="s">
         <v>37</v>
       </c>
@@ -4936,7 +5046,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="133" t="s">
         <v>44</v>
       </c>
@@ -4970,7 +5080,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="121"/>
       <c r="B18" s="157"/>
       <c r="C18" s="140"/>
@@ -4989,7 +5099,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="178"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -5005,7 +5115,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="121" t="s">
         <v>59</v>
       </c>
@@ -5041,7 +5151,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="133" t="s">
         <v>154</v>
       </c>
@@ -5072,7 +5182,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="133" t="s">
         <v>153</v>
       </c>
@@ -5104,7 +5214,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="263" t="s">
         <v>224</v>
       </c>
@@ -5129,7 +5239,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="133" t="s">
         <v>223</v>
       </c>
@@ -5157,7 +5267,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="262" t="s">
         <v>122</v>
       </c>
@@ -5183,7 +5293,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="263" t="s">
         <v>123</v>
       </c>
@@ -5207,7 +5317,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="139"/>
       <c r="B27" s="205"/>
       <c r="C27" s="207"/>
@@ -5227,7 +5337,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="251"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -5247,7 +5357,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="251"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -5268,7 +5378,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="166"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -5288,7 +5398,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="205"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -5305,7 +5415,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="157"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -5324,7 +5434,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="165"/>
       <c r="B33" s="165"/>
       <c r="C33" s="165"/>
@@ -5341,7 +5451,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -5358,7 +5468,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -5373,23 +5483,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -5408,23 +5518,23 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282C577C-53E4-465B-B7DF-A987DD815E39}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="115" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="115" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="223" t="s">
         <v>133</v>
       </c>
@@ -5432,16 +5542,16 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="290" t="s">
+      <c r="F1" s="303" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="290"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
       <c r="K1" s="165"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="121" t="s">
         <v>0</v>
       </c>
@@ -5476,7 +5586,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="170" t="s">
         <v>196</v>
       </c>
@@ -5511,7 +5621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="130" t="s">
         <v>195</v>
       </c>
@@ -5536,7 +5646,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="206"/>
       <c r="B5" s="130" t="s">
         <v>21</v>
@@ -5563,7 +5673,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="130"/>
       <c r="B6" s="130" t="s">
         <v>134</v>
@@ -5592,7 +5702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="247" t="s">
         <v>114</v>
       </c>
@@ -5618,7 +5728,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="170" t="s">
         <v>194</v>
       </c>
@@ -5644,7 +5754,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="130" t="s">
         <v>92</v>
       </c>
@@ -5680,7 +5790,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="130" t="s">
         <v>222</v>
       </c>
@@ -5711,7 +5821,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="130"/>
       <c r="B11" s="130" t="s">
         <v>137</v>
@@ -5729,7 +5839,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="248" t="s">
         <v>113</v>
       </c>
@@ -5753,7 +5863,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130" t="s">
         <v>99</v>
       </c>
@@ -5770,7 +5880,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="130" t="s">
         <v>82</v>
       </c>
@@ -5796,7 +5906,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="157"/>
       <c r="B15" s="256" t="s">
         <v>219</v>
@@ -5816,7 +5926,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="121" t="s">
         <v>37</v>
       </c>
@@ -5849,7 +5959,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="133" t="s">
         <v>44</v>
       </c>
@@ -5883,7 +5993,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="121"/>
       <c r="B18" s="157"/>
       <c r="C18" s="140"/>
@@ -5902,7 +6012,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="178"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -5918,7 +6028,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="121" t="s">
         <v>59</v>
       </c>
@@ -5954,7 +6064,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="133" t="s">
         <v>153</v>
       </c>
@@ -5986,7 +6096,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="263" t="s">
         <v>224</v>
       </c>
@@ -6018,7 +6128,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="133" t="s">
         <v>223</v>
       </c>
@@ -6047,7 +6157,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="133" t="s">
         <v>154</v>
       </c>
@@ -6075,7 +6185,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="262" t="s">
         <v>122</v>
       </c>
@@ -6101,7 +6211,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="263" t="s">
         <v>123</v>
       </c>
@@ -6124,7 +6234,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="139"/>
       <c r="B27" s="205"/>
       <c r="C27" s="207"/>
@@ -6142,7 +6252,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="251"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -6160,7 +6270,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="251"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -6182,7 +6292,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="166"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -6202,7 +6312,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="205"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -6222,7 +6332,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="157"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -6241,7 +6351,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="165"/>
       <c r="B33" s="165"/>
       <c r="C33" s="165"/>
@@ -6258,7 +6368,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -6273,7 +6383,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -6288,23 +6398,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -6322,23 +6432,23 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2BDB1C-DF30-4B6C-946B-083CC977B836}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="115" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="115" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="121" t="s">
         <v>0</v>
       </c>
@@ -6346,16 +6456,16 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="290" t="s">
+      <c r="F1" s="303" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="290"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
       <c r="K1" s="165"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="170" t="s">
         <v>196</v>
       </c>
@@ -6390,7 +6500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="130" t="s">
         <v>195</v>
       </c>
@@ -6425,7 +6535,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="206"/>
       <c r="B4" s="277" t="s">
         <v>238</v>
@@ -6452,7 +6562,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="130"/>
       <c r="B5" s="130" t="s">
         <v>21</v>
@@ -6479,7 +6589,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="247" t="s">
         <v>114</v>
       </c>
@@ -6510,7 +6620,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="170" t="s">
         <v>194</v>
       </c>
@@ -6539,7 +6649,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="130" t="s">
         <v>92</v>
       </c>
@@ -6568,7 +6678,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="130" t="s">
         <v>222</v>
       </c>
@@ -6604,7 +6714,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="130"/>
       <c r="B10" s="130" t="s">
         <v>139</v>
@@ -6634,7 +6744,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="248" t="s">
         <v>113</v>
       </c>
@@ -6658,7 +6768,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="130" t="s">
         <v>99</v>
       </c>
@@ -6680,7 +6790,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130" t="s">
         <v>82</v>
       </c>
@@ -6702,7 +6812,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="157"/>
       <c r="B14" s="224" t="s">
         <v>239</v>
@@ -6724,7 +6834,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="121" t="s">
         <v>37</v>
       </c>
@@ -6746,7 +6856,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="133" t="s">
         <v>44</v>
       </c>
@@ -6782,7 +6892,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="121"/>
       <c r="B17" s="133" t="s">
         <v>45</v>
@@ -6814,7 +6924,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="178"/>
       <c r="B18" s="157"/>
       <c r="C18" s="140"/>
@@ -6834,7 +6944,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="121" t="s">
         <v>59</v>
       </c>
@@ -6852,7 +6962,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="133" t="s">
         <v>153</v>
       </c>
@@ -6888,7 +6998,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="263" t="s">
         <v>224</v>
       </c>
@@ -6920,7 +7030,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="133" t="s">
         <v>223</v>
       </c>
@@ -6952,7 +7062,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="133" t="s">
         <v>154</v>
       </c>
@@ -6982,7 +7092,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="262" t="s">
         <v>122</v>
       </c>
@@ -7012,7 +7122,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="263" t="s">
         <v>123</v>
       </c>
@@ -7036,7 +7146,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="139"/>
       <c r="B26" s="234"/>
       <c r="C26" s="133" t="s">
@@ -7058,7 +7168,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="251"/>
       <c r="B27" s="205"/>
       <c r="C27" s="207"/>
@@ -7076,7 +7186,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="251"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -7093,7 +7203,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="166"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -7113,7 +7223,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="205"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -7133,7 +7243,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="157"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -7153,7 +7263,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="165"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -7170,7 +7280,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="122"/>
       <c r="B33" s="165"/>
       <c r="C33" s="165"/>
@@ -7185,7 +7295,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -7200,7 +7310,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
       <c r="D35" s="122"/>
@@ -7214,23 +7324,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -7248,23 +7358,23 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29362803-B43D-42C8-8917-8269CAB71678}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="115" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="115" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="121" t="s">
         <v>0</v>
       </c>
@@ -7272,16 +7382,16 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="290" t="s">
+      <c r="F1" s="303" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="290"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
       <c r="K1" s="165"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="170" t="s">
         <v>196</v>
       </c>
@@ -7316,7 +7426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="130" t="s">
         <v>195</v>
       </c>
@@ -7351,7 +7461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="206"/>
       <c r="B4" s="277" t="s">
         <v>238</v>
@@ -7380,7 +7490,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="130"/>
       <c r="B5" s="130" t="s">
         <v>21</v>
@@ -7407,7 +7517,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="247" t="s">
         <v>114</v>
       </c>
@@ -7438,7 +7548,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="170" t="s">
         <v>194</v>
       </c>
@@ -7467,7 +7577,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="130" t="s">
         <v>92</v>
       </c>
@@ -7496,7 +7606,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="130" t="s">
         <v>222</v>
       </c>
@@ -7532,7 +7642,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="130"/>
       <c r="B10" s="130" t="s">
         <v>139</v>
@@ -7562,7 +7672,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="248" t="s">
         <v>113</v>
       </c>
@@ -7586,7 +7696,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="130" t="s">
         <v>99</v>
       </c>
@@ -7608,7 +7718,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130" t="s">
         <v>82</v>
       </c>
@@ -7630,7 +7740,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="157"/>
       <c r="B14" s="224" t="s">
         <v>239</v>
@@ -7652,7 +7762,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="121" t="s">
         <v>37</v>
       </c>
@@ -7674,7 +7784,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="133" t="s">
         <v>44</v>
       </c>
@@ -7708,7 +7818,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="121"/>
       <c r="B17" s="133" t="s">
         <v>45</v>
@@ -7740,7 +7850,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="178"/>
       <c r="B18" s="157"/>
       <c r="C18" s="140"/>
@@ -7760,7 +7870,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="121" t="s">
         <v>59</v>
       </c>
@@ -7778,7 +7888,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="133" t="s">
         <v>153</v>
       </c>
@@ -7814,7 +7924,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="263" t="s">
         <v>224</v>
       </c>
@@ -7848,7 +7958,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="133" t="s">
         <v>223</v>
       </c>
@@ -7880,7 +7990,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="133" t="s">
         <v>154</v>
       </c>
@@ -7910,7 +8020,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="262" t="s">
         <v>122</v>
       </c>
@@ -7936,7 +8046,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="250" t="s">
         <v>198</v>
       </c>
@@ -7957,7 +8067,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="139"/>
       <c r="B26" s="234"/>
       <c r="C26" s="133" t="s">
@@ -7979,7 +8089,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="251"/>
       <c r="B27" s="205"/>
       <c r="C27" s="207"/>
@@ -7999,7 +8109,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="251"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -8019,7 +8129,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="166"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -8039,7 +8149,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="205"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -8059,7 +8169,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="157"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -8077,7 +8187,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="165"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -8094,7 +8204,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="122"/>
       <c r="B33" s="165"/>
       <c r="C33" s="165"/>
@@ -8109,7 +8219,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -8124,7 +8234,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
       <c r="D35" s="122"/>
@@ -8138,23 +8248,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -8172,23 +8282,23 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92951B2-73A2-4280-AE54-74A817BAE734}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="115" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="115" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="121" t="s">
         <v>0</v>
       </c>
@@ -8196,16 +8306,16 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="290" t="s">
+      <c r="F1" s="303" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="290"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
       <c r="K1" s="165"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="170" t="s">
         <v>196</v>
       </c>
@@ -8240,7 +8350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="130" t="s">
         <v>195</v>
       </c>
@@ -8275,7 +8385,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="206"/>
       <c r="B4" s="277" t="s">
         <v>238</v>
@@ -8304,7 +8414,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="130"/>
       <c r="B5" s="130" t="s">
         <v>21</v>
@@ -8331,7 +8441,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="247" t="s">
         <v>114</v>
       </c>
@@ -8362,7 +8472,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="130" t="s">
         <v>194</v>
       </c>
@@ -8391,7 +8501,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="130" t="s">
         <v>92</v>
       </c>
@@ -8420,7 +8530,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="256" t="s">
         <v>222</v>
       </c>
@@ -8456,7 +8566,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="130"/>
       <c r="B10" s="130" t="s">
         <v>139</v>
@@ -8486,7 +8596,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="248" t="s">
         <v>113</v>
       </c>
@@ -8510,7 +8620,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="130" t="s">
         <v>99</v>
       </c>
@@ -8532,7 +8642,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130" t="s">
         <v>82</v>
       </c>
@@ -8554,7 +8664,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="157"/>
       <c r="B14" s="224" t="s">
         <v>239</v>
@@ -8576,7 +8686,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="121" t="s">
         <v>37</v>
       </c>
@@ -8598,7 +8708,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="133" t="s">
         <v>44</v>
       </c>
@@ -8632,7 +8742,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="121"/>
       <c r="B17" s="133" t="s">
         <v>45</v>
@@ -8664,7 +8774,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="178"/>
       <c r="B18" s="157"/>
       <c r="C18" s="140"/>
@@ -8684,7 +8794,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="121" t="s">
         <v>59</v>
       </c>
@@ -8702,7 +8812,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="133" t="s">
         <v>153</v>
       </c>
@@ -8738,7 +8848,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="263" t="s">
         <v>224</v>
       </c>
@@ -8772,7 +8882,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="133" t="s">
         <v>223</v>
       </c>
@@ -8804,7 +8914,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="133" t="s">
         <v>154</v>
       </c>
@@ -8834,7 +8944,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="262" t="s">
         <v>122</v>
       </c>
@@ -8860,7 +8970,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="262" t="s">
         <v>198</v>
       </c>
@@ -8881,7 +8991,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="139"/>
       <c r="B26" s="234"/>
       <c r="C26" s="133" t="s">
@@ -8903,7 +9013,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="251"/>
       <c r="B27" s="205"/>
       <c r="C27" s="207"/>
@@ -8923,7 +9033,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="251"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -8943,7 +9053,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="166"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -8963,7 +9073,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="205"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -8983,7 +9093,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="157"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -9001,7 +9111,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="165"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -9018,7 +9128,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="122"/>
       <c r="B33" s="165"/>
       <c r="C33" s="165"/>
@@ -9033,7 +9143,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -9048,7 +9158,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
       <c r="D35" s="122"/>
@@ -9062,23 +9172,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -9093,38 +9203,38 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C160085-DF24-4B29-9BA4-52700F925B9C}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="115" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="115" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="133"/>
       <c r="B1" s="244"/>
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="290" t="s">
+      <c r="F1" s="303" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="290"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
       <c r="K1" s="165"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="121" t="s">
         <v>0</v>
       </c>
@@ -9159,7 +9269,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="130" t="s">
         <v>131</v>
       </c>
@@ -9194,7 +9304,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="130" t="s">
         <v>195</v>
       </c>
@@ -9217,11 +9327,11 @@
       <c r="J4" s="133" t="s">
         <v>244</v>
       </c>
-      <c r="K4" s="292" t="s">
+      <c r="K4" s="289" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="206"/>
       <c r="B5" s="130" t="s">
         <v>21</v>
@@ -9248,7 +9358,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="130"/>
       <c r="B6" s="130" t="s">
         <v>134</v>
@@ -9277,7 +9387,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="247" t="s">
         <v>114</v>
       </c>
@@ -9299,14 +9409,14 @@
       <c r="I7" s="150" t="s">
         <v>66</v>
       </c>
-      <c r="J7" s="291" t="s">
+      <c r="J7" s="288" t="s">
         <v>186</v>
       </c>
       <c r="K7" s="250" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="130" t="s">
         <v>194</v>
       </c>
@@ -9335,7 +9445,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="130" t="s">
         <v>92</v>
       </c>
@@ -9371,7 +9481,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="170" t="s">
         <v>222</v>
       </c>
@@ -9403,7 +9513,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="130"/>
       <c r="B11" s="130" t="s">
         <v>137</v>
@@ -9425,7 +9535,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="248" t="s">
         <v>113</v>
       </c>
@@ -9449,7 +9559,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130" t="s">
         <v>99</v>
       </c>
@@ -9471,7 +9581,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="130" t="s">
         <v>82</v>
       </c>
@@ -9497,7 +9607,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="157"/>
       <c r="B15" s="283" t="s">
         <v>239</v>
@@ -9519,7 +9629,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="121" t="s">
         <v>37</v>
       </c>
@@ -9557,7 +9667,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="133" t="s">
         <v>44</v>
       </c>
@@ -9593,7 +9703,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="121"/>
       <c r="B18" s="157"/>
       <c r="C18" s="140"/>
@@ -9612,7 +9722,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="178"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -9628,7 +9738,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="121" t="s">
         <v>59</v>
       </c>
@@ -9664,7 +9774,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="267" t="s">
         <v>153</v>
       </c>
@@ -9694,7 +9804,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="263" t="s">
         <v>224</v>
       </c>
@@ -9726,7 +9836,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="133" t="s">
         <v>223</v>
       </c>
@@ -9753,7 +9863,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="143" t="s">
         <v>154</v>
       </c>
@@ -9776,7 +9886,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="250" t="s">
         <v>122</v>
       </c>
@@ -9798,7 +9908,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="250" t="s">
         <v>198</v>
       </c>
@@ -9822,7 +9932,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="139"/>
       <c r="B27" s="205"/>
       <c r="C27" s="284"/>
@@ -9842,7 +9952,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="251"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -9860,7 +9970,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="251"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -9882,7 +9992,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="166"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -9900,7 +10010,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="205"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -9918,7 +10028,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="157"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -9935,7 +10045,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="165"/>
       <c r="B33" s="165"/>
       <c r="C33" s="165"/>
@@ -9950,7 +10060,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -9964,7 +10074,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -9979,23 +10089,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -10014,38 +10124,38 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9734630C-E61A-4DB2-9CE7-7CCFB6DC35A4}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="115" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="115" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="133"/>
       <c r="B1" s="244"/>
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="290" t="s">
+      <c r="F1" s="303" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="290"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
-      <c r="J1" s="293"/>
+      <c r="J1" s="290"/>
       <c r="K1" s="165"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="121" t="s">
         <v>0</v>
       </c>
@@ -10080,7 +10190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="130" t="s">
         <v>131</v>
       </c>
@@ -10108,14 +10218,14 @@
       <c r="I3" s="130" t="s">
         <v>98</v>
       </c>
-      <c r="J3" s="294" t="s">
+      <c r="J3" s="291" t="s">
         <v>77</v>
       </c>
       <c r="K3" s="223" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="130" t="s">
         <v>195</v>
       </c>
@@ -10144,7 +10254,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="206"/>
       <c r="B5" s="130" t="s">
         <v>21</v>
@@ -10171,7 +10281,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="130"/>
       <c r="B6" s="130" t="s">
         <v>134</v>
@@ -10200,7 +10310,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="247" t="s">
         <v>114</v>
       </c>
@@ -10222,14 +10332,14 @@
       <c r="I7" s="150" t="s">
         <v>66</v>
       </c>
-      <c r="J7" s="295" t="s">
+      <c r="J7" s="292" t="s">
         <v>186</v>
       </c>
       <c r="K7" s="255" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="130" t="s">
         <v>194</v>
       </c>
@@ -10251,14 +10361,14 @@
       <c r="I8" s="223" t="s">
         <v>213</v>
       </c>
-      <c r="J8" s="294" t="s">
+      <c r="J8" s="291" t="s">
         <v>214</v>
       </c>
       <c r="K8" s="139" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="130" t="s">
         <v>92</v>
       </c>
@@ -10286,7 +10396,7 @@
       <c r="I9" s="133" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="296" t="s">
+      <c r="J9" s="293" t="s">
         <v>110</v>
       </c>
       <c r="K9" s="150" t="s">
@@ -10294,7 +10404,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="170" t="s">
         <v>222</v>
       </c>
@@ -10324,7 +10434,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="130"/>
       <c r="B11" s="130" t="s">
         <v>137</v>
@@ -10338,7 +10448,7 @@
       <c r="G11" s="234"/>
       <c r="H11" s="122"/>
       <c r="I11" s="140"/>
-      <c r="J11" s="297" t="s">
+      <c r="J11" s="294" t="s">
         <v>232</v>
       </c>
       <c r="K11" s="224" t="s">
@@ -10346,7 +10456,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="248" t="s">
         <v>113</v>
       </c>
@@ -10368,7 +10478,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130" t="s">
         <v>99</v>
       </c>
@@ -10382,7 +10492,7 @@
       <c r="G13" s="140"/>
       <c r="H13" s="140"/>
       <c r="I13" s="139"/>
-      <c r="J13" s="297" t="s">
+      <c r="J13" s="294" t="s">
         <v>231</v>
       </c>
       <c r="K13" s="150" t="s">
@@ -10390,7 +10500,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="130" t="s">
         <v>82</v>
       </c>
@@ -10406,7 +10516,7 @@
       <c r="G14" s="121"/>
       <c r="H14" s="160"/>
       <c r="I14" s="60"/>
-      <c r="J14" s="296" t="s">
+      <c r="J14" s="293" t="s">
         <v>85</v>
       </c>
       <c r="K14" s="151" t="s">
@@ -10416,7 +10526,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="157"/>
       <c r="B15" s="283" t="s">
         <v>239</v>
@@ -10428,7 +10538,7 @@
       <c r="G15" s="150"/>
       <c r="H15" s="166"/>
       <c r="I15" s="140"/>
-      <c r="J15" s="296" t="s">
+      <c r="J15" s="293" t="s">
         <v>31</v>
       </c>
       <c r="K15" s="150" t="s">
@@ -10438,7 +10548,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="121" t="s">
         <v>37</v>
       </c>
@@ -10476,7 +10586,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="133" t="s">
         <v>44</v>
       </c>
@@ -10510,7 +10620,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="121"/>
       <c r="B18" s="157"/>
       <c r="C18" s="140"/>
@@ -10529,7 +10639,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="178"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -10545,7 +10655,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="121" t="s">
         <v>59</v>
       </c>
@@ -10581,7 +10691,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="267" t="s">
         <v>153</v>
       </c>
@@ -10615,7 +10725,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="263" t="s">
         <v>224</v>
       </c>
@@ -10647,13 +10757,14 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="133" t="s">
         <v>223</v>
       </c>
       <c r="B23" s="267" t="s">
         <v>133</v>
       </c>
+      <c r="C23" s="234"/>
       <c r="D23" s="141" t="s">
         <v>111</v>
       </c>
@@ -10674,11 +10785,12 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="143" t="s">
         <v>154</v>
       </c>
       <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
       <c r="D24" s="141" t="s">
         <v>165</v>
       </c>
@@ -10697,12 +10809,12 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="250" t="s">
         <v>122</v>
       </c>
       <c r="B25" s="234"/>
-      <c r="C25" s="270"/>
+      <c r="C25" s="202"/>
       <c r="D25" s="234"/>
       <c r="E25" s="166"/>
       <c r="F25" s="157"/>
@@ -10719,7 +10831,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="250" t="s">
         <v>198</v>
       </c>
@@ -10741,7 +10853,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="139"/>
       <c r="B27" s="205"/>
       <c r="C27" s="284"/>
@@ -10759,7 +10871,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="251"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -10777,7 +10889,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="251"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -10799,7 +10911,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="166"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -10819,7 +10931,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="205"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -10836,7 +10948,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="157"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -10853,7 +10965,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="165"/>
       <c r="B33" s="165"/>
       <c r="C33" s="165"/>
@@ -10868,7 +10980,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -10882,7 +10994,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -10897,23 +11009,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -10929,40 +11041,1609 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B414951A-91D4-4146-9406-59783AF94A29}">
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" style="234" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="234" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="234" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="234" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="234" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="234" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="234" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="234" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="234" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="234" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="234" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="234"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="295"/>
+      <c r="F1" s="303" t="s">
+        <v>248</v>
+      </c>
+      <c r="G1" s="303"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:11" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="130" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="143" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="143" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="133" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="143" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="223" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="133"/>
+      <c r="G4" s="133" t="s">
+        <v>243</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="250" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="133" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>241</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="170" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="288" t="s">
+        <v>186</v>
+      </c>
+      <c r="K7" s="255" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="130" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="141" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="223" t="s">
+        <v>213</v>
+      </c>
+      <c r="J8" s="143" t="s">
+        <v>214</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="224" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="141" t="s">
+        <v>110</v>
+      </c>
+      <c r="K9" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="170" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="130" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="143" t="s">
+        <v>207</v>
+      </c>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="K10" s="224" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="165"/>
+      <c r="D11" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="267" t="s">
+        <v>232</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="249"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="59"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="267" t="s">
+        <v>231</v>
+      </c>
+      <c r="K13" s="151" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="151"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157">
+        <v>0</v>
+      </c>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="141" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="150" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="141" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="133" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="133" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="159" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="267" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="143" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="267" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="263" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>229</v>
+      </c>
+      <c r="C22" s="139" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>202</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="133" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23" s="267" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" s="141" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="250" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>125</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="143" t="s">
+        <v>154</v>
+      </c>
+      <c r="D24" s="141" t="s">
+        <v>165</v>
+      </c>
+      <c r="H24" s="130"/>
+      <c r="I24" s="238" t="s">
+        <v>52</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="250" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="202"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="250" t="s">
+        <v>198</v>
+      </c>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="236" t="s">
+        <v>56</v>
+      </c>
+      <c r="J26" s="193" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="139"/>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="J27" s="296" t="s">
+        <v>84</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="J28" s="207" t="s">
+        <v>127</v>
+      </c>
+      <c r="K28" s="240"/>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="139"/>
+      <c r="H29" s="178"/>
+      <c r="J29" s="296" t="s">
+        <v>208</v>
+      </c>
+      <c r="K29" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="178"/>
+      <c r="J30" s="193" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="178"/>
+      <c r="J31" s="193" t="s">
+        <v>238</v>
+      </c>
+      <c r="K31" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="157"/>
+      <c r="B32" s="157"/>
+      <c r="C32" s="157"/>
+      <c r="D32" s="157"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="157"/>
+      <c r="G32" s="166"/>
+      <c r="H32" s="160"/>
+      <c r="I32" s="237"/>
+      <c r="J32" s="207" t="s">
+        <v>239</v>
+      </c>
+      <c r="K32" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="165"/>
+      <c r="B33" s="165"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="252"/>
+      <c r="E33" s="244"/>
+      <c r="F33" s="244"/>
+      <c r="G33" s="244"/>
+      <c r="H33" s="244"/>
+      <c r="I33" s="238"/>
+      <c r="K33" s="242"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D34" s="252"/>
+      <c r="H34" s="252"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K4:K16">
+    <sortCondition ref="K3:K16"/>
+  </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D107F6B5-AA48-44F1-9BCD-A41C5D523430}">
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" style="234" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" style="234" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="234" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="234" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="234" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="234" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="234" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="234" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="234" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="234" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="234" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="234"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="297"/>
+      <c r="F1" s="303" t="s">
+        <v>248</v>
+      </c>
+      <c r="G1" s="303"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="130" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="133" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="143" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="133" t="s">
+        <v>243</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="224" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>241</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="288" t="s">
+        <v>186</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="130" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="224" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="141" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="223" t="s">
+        <v>213</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="150"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>252</v>
+      </c>
+      <c r="K9" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="138"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="170" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="143" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="143" t="s">
+        <v>207</v>
+      </c>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="224"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="143" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="143" t="s">
+        <v>254</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>219</v>
+      </c>
+      <c r="D12" s="59"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="143" t="s">
+        <v>255</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="143" t="s">
+        <v>176</v>
+      </c>
+      <c r="K13" s="170" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="151"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="141" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="223" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="133" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="133"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="133" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="159" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="267" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>250</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="143" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="263" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="133" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23" s="267" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" s="267" t="s">
+        <v>232</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="267" t="s">
+        <v>251</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>125</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="143" t="s">
+        <v>154</v>
+      </c>
+      <c r="D24" s="141"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="238" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="250" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="202"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="250" t="s">
+        <v>198</v>
+      </c>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>110</v>
+      </c>
+      <c r="J26" s="193" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="139"/>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="I27" s="237" t="s">
+        <v>183</v>
+      </c>
+      <c r="J27" s="207" t="s">
+        <v>127</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="I28" s="237" t="s">
+        <v>171</v>
+      </c>
+      <c r="J28" s="296" t="s">
+        <v>208</v>
+      </c>
+      <c r="K28" s="240"/>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J29" s="193" t="s">
+        <v>257</v>
+      </c>
+      <c r="K29" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="J30" s="193" t="s">
+        <v>258</v>
+      </c>
+      <c r="K30" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="207" t="s">
+        <v>158</v>
+      </c>
+      <c r="K31" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="157"/>
+      <c r="B32" s="157"/>
+      <c r="C32" s="157"/>
+      <c r="D32" s="157"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="157"/>
+      <c r="H32" s="160"/>
+      <c r="I32" s="238"/>
+      <c r="K32" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="165"/>
+      <c r="B33" s="165"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="252"/>
+      <c r="E33" s="244"/>
+      <c r="F33" s="244"/>
+      <c r="H33" s="244"/>
+      <c r="I33" s="238"/>
+      <c r="K33" s="242"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D34" s="252"/>
+      <c r="H34" s="252"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A76CFE-4E0A-48D9-BC59-C68444162F7C}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="288" t="s">
+      <c r="F1" s="301" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="289"/>
+      <c r="G1" s="302"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="13"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -10997,7 +12678,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>131</v>
       </c>
@@ -11032,7 +12713,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>132</v>
       </c>
@@ -11063,7 +12744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="30"/>
       <c r="B5" s="15" t="s">
         <v>121</v>
@@ -11090,7 +12771,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="113"/>
       <c r="B6" s="107" t="s">
         <v>129</v>
@@ -11119,7 +12800,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="40" t="s">
         <v>114</v>
       </c>
@@ -11148,7 +12829,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>107</v>
       </c>
@@ -11177,7 +12858,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
         <v>92</v>
       </c>
@@ -11211,7 +12892,7 @@
       </c>
       <c r="M9" s="7"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>124</v>
       </c>
@@ -11241,7 +12922,7 @@
       </c>
       <c r="M10" s="7"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="22"/>
       <c r="B11" s="15" t="s">
         <v>108</v>
@@ -11263,7 +12944,7 @@
       </c>
       <c r="M11" s="7"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="54" t="s">
         <v>113</v>
       </c>
@@ -11286,7 +12967,7 @@
       </c>
       <c r="M12" s="7"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
         <v>99</v>
       </c>
@@ -11307,7 +12988,7 @@
       </c>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>82</v>
       </c>
@@ -11331,7 +13012,7 @@
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="62"/>
       <c r="B15" s="36"/>
       <c r="C15" s="25"/>
@@ -11349,7 +13030,7 @@
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
@@ -11383,7 +13064,7 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="67" t="s">
         <v>44</v>
       </c>
@@ -11415,7 +13096,7 @@
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="42"/>
       <c r="C18" s="45"/>
@@ -11435,7 +13116,7 @@
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="70"/>
       <c r="B19" s="6"/>
       <c r="C19" s="42"/>
@@ -11451,7 +13132,7 @@
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
     </row>
-    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>59</v>
       </c>
@@ -11487,7 +13168,7 @@
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="80" t="s">
         <v>154</v>
       </c>
@@ -11521,7 +13202,7 @@
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="80" t="s">
         <v>153</v>
       </c>
@@ -11551,7 +13232,7 @@
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="111" t="s">
         <v>117</v>
       </c>
@@ -11579,7 +13260,7 @@
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="112" t="s">
         <v>126</v>
       </c>
@@ -11603,7 +13284,7 @@
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="86" t="s">
         <v>122</v>
       </c>
@@ -11625,7 +13306,7 @@
       <c r="N25" s="7"/>
       <c r="O25" s="7"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="86" t="s">
         <v>123</v>
       </c>
@@ -11647,7 +13328,7 @@
       <c r="N26" s="7"/>
       <c r="O26" s="7"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="77"/>
       <c r="B27" s="90"/>
       <c r="C27" s="83"/>
@@ -11667,7 +13348,7 @@
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="80"/>
       <c r="B28" s="42"/>
       <c r="C28" s="78"/>
@@ -11687,7 +13368,7 @@
       <c r="N28" s="7"/>
       <c r="O28" s="7"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="80"/>
       <c r="B29" s="42"/>
       <c r="C29" s="91"/>
@@ -11709,7 +13390,7 @@
       <c r="N29" s="7"/>
       <c r="O29" s="7"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="95"/>
       <c r="B30" s="42"/>
       <c r="C30" s="91"/>
@@ -11729,7 +13410,7 @@
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="96"/>
       <c r="B31" s="42"/>
       <c r="C31" s="91"/>
@@ -11749,7 +13430,7 @@
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="62"/>
       <c r="B32" s="42"/>
       <c r="C32" s="42"/>
@@ -11768,7 +13449,7 @@
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
     </row>
-    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="98"/>
       <c r="B33" s="99"/>
       <c r="C33" s="99"/>
@@ -11783,7 +13464,7 @@
       <c r="M33" s="7"/>
       <c r="N33" s="7"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -11798,7 +13479,7 @@
       <c r="M34" s="7"/>
       <c r="N34" s="7"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -11813,25 +13494,803 @@
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="7"/>
       <c r="N36" s="7"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92FC548-FF44-4B02-AFA4-A6ACA9FECCCA}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="298"/>
+      <c r="F1" s="303" t="s">
+        <v>260</v>
+      </c>
+      <c r="G1" s="303"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="130" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="133" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="143" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="F4" s="234"/>
+      <c r="G4" s="133" t="s">
+        <v>243</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="224" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>241</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="288" t="s">
+        <v>186</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="130" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="I8" s="223" t="s">
+        <v>213</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="224" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="143" t="s">
+        <v>259</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>252</v>
+      </c>
+      <c r="K9" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="170" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="143" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="234"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="143" t="s">
+        <v>254</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="143" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="143" t="s">
+        <v>255</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="143" t="s">
+        <v>176</v>
+      </c>
+      <c r="K13" s="170" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="151"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="141" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="223" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="234"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="133"/>
+      <c r="K16" s="234"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="133" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="159" t="s">
+        <v>227</v>
+      </c>
+      <c r="J17" s="234"/>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="267" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>250</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="143" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="263" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" s="267" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="133" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23" s="234"/>
+      <c r="C23" s="234"/>
+      <c r="D23" s="267" t="s">
+        <v>232</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="267" t="s">
+        <v>251</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>125</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="143" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="141"/>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="234"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="238" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="250" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="250" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="234"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" s="193" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="139"/>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J27" s="207" t="s">
+        <v>127</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237" t="s">
+        <v>56</v>
+      </c>
+      <c r="J28" s="193" t="s">
+        <v>257</v>
+      </c>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237"/>
+      <c r="J29" s="207" t="s">
+        <v>158</v>
+      </c>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="237"/>
+      <c r="J30" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11845,38 +14304,38 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAC2020D-2348-4A50-8C52-2DF87069EFE1}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" style="115" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" style="115" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="116"/>
       <c r="B1" s="117"/>
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="288" t="s">
+      <c r="F1" s="301" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="289"/>
+      <c r="G1" s="302"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
       <c r="K1" s="128"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="120" t="s">
         <v>0</v>
       </c>
@@ -11911,7 +14370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="137" t="s">
         <v>131</v>
       </c>
@@ -11946,7 +14405,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="129" t="s">
         <v>132</v>
       </c>
@@ -11977,7 +14436,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="145"/>
       <c r="B5" s="130" t="s">
         <v>121</v>
@@ -12004,7 +14463,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="230"/>
       <c r="B6" s="224" t="s">
         <v>129</v>
@@ -12033,7 +14492,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="155" t="s">
         <v>114</v>
       </c>
@@ -12062,7 +14521,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="129" t="s">
         <v>107</v>
       </c>
@@ -12091,7 +14550,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="137" t="s">
         <v>92</v>
       </c>
@@ -12125,7 +14584,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="137" t="s">
         <v>124</v>
       </c>
@@ -12155,7 +14614,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="137"/>
       <c r="B11" s="130" t="s">
         <v>108</v>
@@ -12177,7 +14636,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="169" t="s">
         <v>113</v>
       </c>
@@ -12200,7 +14659,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="137" t="s">
         <v>99</v>
       </c>
@@ -12221,7 +14680,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="137" t="s">
         <v>82</v>
       </c>
@@ -12245,7 +14704,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="177"/>
       <c r="B15" s="151"/>
       <c r="C15" s="140"/>
@@ -12263,7 +14722,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="120" t="s">
         <v>37</v>
       </c>
@@ -12299,7 +14758,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="182" t="s">
         <v>44</v>
       </c>
@@ -12331,7 +14790,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="120"/>
       <c r="B18" s="157"/>
       <c r="C18" s="160"/>
@@ -12351,7 +14810,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="185"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -12367,7 +14826,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="120" t="s">
         <v>59</v>
       </c>
@@ -12403,7 +14862,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="195" t="s">
         <v>154</v>
       </c>
@@ -12437,7 +14896,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="195" t="s">
         <v>153</v>
       </c>
@@ -12469,7 +14928,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="228" t="s">
         <v>117</v>
       </c>
@@ -12497,7 +14956,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="229" t="s">
         <v>126</v>
       </c>
@@ -12519,7 +14978,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="201" t="s">
         <v>122</v>
       </c>
@@ -12541,7 +15000,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="201" t="s">
         <v>123</v>
       </c>
@@ -12563,7 +15022,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="192"/>
       <c r="B27" s="205"/>
       <c r="C27" s="198"/>
@@ -12583,7 +15042,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="195"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -12601,7 +15060,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="195"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -12623,7 +15082,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="211"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -12643,7 +15102,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="212"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -12663,7 +15122,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="177"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -12682,7 +15141,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="214"/>
       <c r="B33" s="215"/>
       <c r="C33" s="215"/>
@@ -12697,7 +15156,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -12712,7 +15171,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -12727,23 +15186,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -12759,38 +15218,38 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B29AE2-4E84-4C86-B6F8-6135B45433DA}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" style="115" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" style="115" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="116"/>
       <c r="B1" s="117"/>
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="288" t="s">
+      <c r="F1" s="301" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="289"/>
+      <c r="G1" s="302"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
       <c r="K1" s="128"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="120" t="s">
         <v>0</v>
       </c>
@@ -12825,7 +15284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="129" t="s">
         <v>196</v>
       </c>
@@ -12860,7 +15319,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="137" t="s">
         <v>195</v>
       </c>
@@ -12891,7 +15350,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="145"/>
       <c r="B5" s="130" t="s">
         <v>121</v>
@@ -12918,7 +15377,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="230"/>
       <c r="B6" s="224" t="s">
         <v>129</v>
@@ -12947,7 +15406,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="155" t="s">
         <v>114</v>
       </c>
@@ -12976,7 +15435,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="137" t="s">
         <v>194</v>
       </c>
@@ -13005,7 +15464,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="137" t="s">
         <v>92</v>
       </c>
@@ -13041,7 +15500,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="129" t="s">
         <v>193</v>
       </c>
@@ -13073,7 +15532,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="137"/>
       <c r="B11" s="130" t="s">
         <v>108</v>
@@ -13097,7 +15556,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="169" t="s">
         <v>113</v>
       </c>
@@ -13120,7 +15579,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="137" t="s">
         <v>99</v>
       </c>
@@ -13141,7 +15600,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="137" t="s">
         <v>82</v>
       </c>
@@ -13165,7 +15624,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="177"/>
       <c r="B15" s="151"/>
       <c r="C15" s="140"/>
@@ -13183,7 +15642,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="120" t="s">
         <v>37</v>
       </c>
@@ -13219,7 +15678,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="182" t="s">
         <v>44</v>
       </c>
@@ -13251,7 +15710,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="120"/>
       <c r="B18" s="157"/>
       <c r="C18" s="160"/>
@@ -13271,7 +15730,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="185"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -13287,7 +15746,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="120" t="s">
         <v>59</v>
       </c>
@@ -13323,7 +15782,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="201" t="s">
         <v>200</v>
       </c>
@@ -13357,7 +15816,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="201" t="s">
         <v>199</v>
       </c>
@@ -13387,7 +15846,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="228" t="s">
         <v>117</v>
       </c>
@@ -13413,7 +15872,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="229" t="s">
         <v>126</v>
       </c>
@@ -13435,7 +15894,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="228" t="s">
         <v>197</v>
       </c>
@@ -13457,7 +15916,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="228" t="s">
         <v>198</v>
       </c>
@@ -13479,7 +15938,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="192"/>
       <c r="B27" s="205"/>
       <c r="C27" s="198"/>
@@ -13499,7 +15958,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="195"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -13517,7 +15976,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="195"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -13539,7 +15998,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="211"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -13559,7 +16018,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="212"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -13579,7 +16038,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="177"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -13596,7 +16055,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="214"/>
       <c r="B33" s="215"/>
       <c r="C33" s="215"/>
@@ -13611,7 +16070,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -13626,7 +16085,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -13641,23 +16100,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -13673,38 +16132,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2521864C-D4F0-4810-846D-2C983B810699}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" style="115" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" style="115" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="116"/>
       <c r="B1" s="117"/>
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="288" t="s">
+      <c r="F1" s="301" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="289"/>
+      <c r="G1" s="302"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
       <c r="K1" s="128"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="120" t="s">
         <v>0</v>
       </c>
@@ -13739,7 +16198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="129" t="s">
         <v>196</v>
       </c>
@@ -13774,7 +16233,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="137" t="s">
         <v>195</v>
       </c>
@@ -13805,7 +16264,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="145"/>
       <c r="B5" s="224" t="s">
         <v>129</v>
@@ -13832,7 +16291,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="230"/>
       <c r="B6" s="130" t="s">
         <v>106</v>
@@ -13861,7 +16320,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="155" t="s">
         <v>114</v>
       </c>
@@ -13890,7 +16349,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="137" t="s">
         <v>194</v>
       </c>
@@ -13919,7 +16378,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="137" t="s">
         <v>92</v>
       </c>
@@ -13955,7 +16414,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="129" t="s">
         <v>193</v>
       </c>
@@ -13987,7 +16446,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="137"/>
       <c r="B11" s="130" t="s">
         <v>95</v>
@@ -14011,7 +16470,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="169" t="s">
         <v>113</v>
       </c>
@@ -14036,7 +16495,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="137" t="s">
         <v>99</v>
       </c>
@@ -14057,7 +16516,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="137" t="s">
         <v>82</v>
       </c>
@@ -14079,7 +16538,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="177"/>
       <c r="B15" s="151"/>
       <c r="C15" s="140"/>
@@ -14097,7 +16556,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="120" t="s">
         <v>37</v>
       </c>
@@ -14133,7 +16592,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="182" t="s">
         <v>44</v>
       </c>
@@ -14165,7 +16624,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="120"/>
       <c r="B18" s="157"/>
       <c r="C18" s="160"/>
@@ -14185,7 +16644,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="185"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -14201,7 +16660,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="120" t="s">
         <v>59</v>
       </c>
@@ -14237,7 +16696,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="201" t="s">
         <v>200</v>
       </c>
@@ -14271,7 +16730,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="201" t="s">
         <v>199</v>
       </c>
@@ -14301,7 +16760,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="228" t="s">
         <v>117</v>
       </c>
@@ -14325,7 +16784,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="229" t="s">
         <v>126</v>
       </c>
@@ -14347,7 +16806,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="228" t="s">
         <v>197</v>
       </c>
@@ -14369,7 +16828,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="228" t="s">
         <v>198</v>
       </c>
@@ -14391,7 +16850,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="192"/>
       <c r="B27" s="205"/>
       <c r="C27" s="198"/>
@@ -14411,7 +16870,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="195"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -14431,7 +16890,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="195"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -14453,7 +16912,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="211"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -14473,7 +16932,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="212"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -14493,7 +16952,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="177"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -14512,7 +16971,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="214"/>
       <c r="B33" s="215"/>
       <c r="C33" s="215"/>
@@ -14527,7 +16986,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -14542,7 +17001,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -14557,23 +17016,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -14589,38 +17048,38 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{275C2A9B-2B37-4E63-9D4B-FC6314DD51CA}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.81640625" style="115" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" style="115" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="116"/>
       <c r="B1" s="117"/>
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="288" t="s">
+      <c r="F1" s="301" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="289"/>
+      <c r="G1" s="302"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
       <c r="K1" s="128"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="120" t="s">
         <v>0</v>
       </c>
@@ -14655,7 +17114,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="129" t="s">
         <v>196</v>
       </c>
@@ -14690,7 +17149,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="137" t="s">
         <v>195</v>
       </c>
@@ -14719,7 +17178,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="145"/>
       <c r="B5" s="130" t="s">
         <v>121</v>
@@ -14746,7 +17205,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="230"/>
       <c r="B6" s="224" t="s">
         <v>129</v>
@@ -14775,7 +17234,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="155" t="s">
         <v>114</v>
       </c>
@@ -14804,7 +17263,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="137" t="s">
         <v>194</v>
       </c>
@@ -14833,7 +17292,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="137" t="s">
         <v>92</v>
       </c>
@@ -14869,7 +17328,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="129" t="s">
         <v>193</v>
       </c>
@@ -14901,7 +17360,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="137"/>
       <c r="B11" s="130" t="s">
         <v>108</v>
@@ -14925,7 +17384,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="169" t="s">
         <v>113</v>
       </c>
@@ -14948,7 +17407,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="137" t="s">
         <v>99</v>
       </c>
@@ -14969,7 +17428,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="137" t="s">
         <v>82</v>
       </c>
@@ -14995,7 +17454,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="177"/>
       <c r="B15" s="151"/>
       <c r="C15" s="140"/>
@@ -15013,7 +17472,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="120" t="s">
         <v>37</v>
       </c>
@@ -15049,7 +17508,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="182" t="s">
         <v>44</v>
       </c>
@@ -15081,7 +17540,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="120"/>
       <c r="B18" s="157"/>
       <c r="C18" s="160"/>
@@ -15101,7 +17560,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="185"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -15117,7 +17576,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="120" t="s">
         <v>59</v>
       </c>
@@ -15153,7 +17612,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="201" t="s">
         <v>200</v>
       </c>
@@ -15187,7 +17646,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="201" t="s">
         <v>199</v>
       </c>
@@ -15219,7 +17678,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="228" t="s">
         <v>117</v>
       </c>
@@ -15245,7 +17704,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="229" t="s">
         <v>126</v>
       </c>
@@ -15267,7 +17726,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="228" t="s">
         <v>197</v>
       </c>
@@ -15289,7 +17748,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="228" t="s">
         <v>198</v>
       </c>
@@ -15311,7 +17770,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="192"/>
       <c r="B27" s="205"/>
       <c r="C27" s="198"/>
@@ -15331,7 +17790,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="195"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -15351,7 +17810,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="195"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -15373,7 +17832,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="211"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -15393,7 +17852,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="212"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -15413,7 +17872,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="177"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -15430,7 +17889,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="214"/>
       <c r="B33" s="215"/>
       <c r="C33" s="215"/>
@@ -15445,7 +17904,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -15460,7 +17919,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -15475,23 +17934,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -15507,38 +17966,38 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CECA119B-CB52-44B0-AD30-7AB8A2FB10B6}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="115" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="115" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="243"/>
       <c r="B1" s="244"/>
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="290" t="s">
+      <c r="F1" s="303" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="290"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
       <c r="K1" s="165"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="121" t="s">
         <v>0</v>
       </c>
@@ -15573,7 +18032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="170" t="s">
         <v>196</v>
       </c>
@@ -15608,7 +18067,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="130" t="s">
         <v>195</v>
       </c>
@@ -15637,7 +18096,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="206"/>
       <c r="B5" s="130" t="s">
         <v>21</v>
@@ -15664,7 +18123,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="130"/>
       <c r="B6" s="130" t="s">
         <v>134</v>
@@ -15693,7 +18152,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="247" t="s">
         <v>114</v>
       </c>
@@ -15722,7 +18181,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="130" t="s">
         <v>194</v>
       </c>
@@ -15751,7 +18210,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="130" t="s">
         <v>92</v>
       </c>
@@ -15784,7 +18243,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="170" t="s">
         <v>193</v>
       </c>
@@ -15814,7 +18273,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="130"/>
       <c r="B11" s="130" t="s">
         <v>137</v>
@@ -15836,7 +18295,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="248" t="s">
         <v>113</v>
       </c>
@@ -15857,7 +18316,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130" t="s">
         <v>99</v>
       </c>
@@ -15877,7 +18336,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="130" t="s">
         <v>82</v>
       </c>
@@ -15903,7 +18362,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="157"/>
       <c r="B15" s="256" t="s">
         <v>219</v>
@@ -15923,7 +18382,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="121" t="s">
         <v>37</v>
       </c>
@@ -15959,7 +18418,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="133" t="s">
         <v>44</v>
       </c>
@@ -15993,7 +18452,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="121"/>
       <c r="B18" s="157"/>
       <c r="C18" s="160"/>
@@ -16013,7 +18472,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="178"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -16029,7 +18488,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="121" t="s">
         <v>59</v>
       </c>
@@ -16065,7 +18524,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="143" t="s">
         <v>200</v>
       </c>
@@ -16096,7 +18555,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="143" t="s">
         <v>199</v>
       </c>
@@ -16125,7 +18584,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="250" t="s">
         <v>117</v>
       </c>
@@ -16153,7 +18612,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="143" t="s">
         <v>126</v>
       </c>
@@ -16179,7 +18638,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="250" t="s">
         <v>197</v>
       </c>
@@ -16200,7 +18659,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="250" t="s">
         <v>198</v>
       </c>
@@ -16222,7 +18681,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="139"/>
       <c r="B27" s="205"/>
       <c r="C27" s="207"/>
@@ -16242,7 +18701,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="251"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -16262,7 +18721,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="251"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -16286,7 +18745,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="166"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -16308,7 +18767,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="205"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -16328,7 +18787,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="157"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -16345,7 +18804,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="165"/>
       <c r="B33" s="165"/>
       <c r="C33" s="165"/>
@@ -16360,7 +18819,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -16375,7 +18834,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -16390,23 +18849,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -16425,38 +18884,38 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC09C5B-F106-473B-B96F-830A4481458B}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="115" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="115" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="243"/>
       <c r="B1" s="244"/>
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="290" t="s">
+      <c r="F1" s="303" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="290"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
       <c r="K1" s="165"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="121" t="s">
         <v>0</v>
       </c>
@@ -16491,7 +18950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="170" t="s">
         <v>196</v>
       </c>
@@ -16526,7 +18985,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="130" t="s">
         <v>195</v>
       </c>
@@ -16552,7 +19011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="206"/>
       <c r="B5" s="130" t="s">
         <v>121</v>
@@ -16579,7 +19038,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="130"/>
       <c r="B6" s="224" t="s">
         <v>158</v>
@@ -16605,7 +19064,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="247" t="s">
         <v>114</v>
       </c>
@@ -16631,7 +19090,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="130" t="s">
         <v>194</v>
       </c>
@@ -16660,7 +19119,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="130" t="s">
         <v>92</v>
       </c>
@@ -16696,7 +19155,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="170" t="s">
         <v>193</v>
       </c>
@@ -16728,7 +19187,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="130"/>
       <c r="B11" s="130" t="s">
         <v>108</v>
@@ -16750,7 +19209,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="248" t="s">
         <v>113</v>
       </c>
@@ -16774,7 +19233,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130" t="s">
         <v>99</v>
       </c>
@@ -16796,7 +19255,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="130" t="s">
         <v>82</v>
       </c>
@@ -16822,7 +19281,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="157"/>
       <c r="B15" s="151"/>
       <c r="C15" s="140"/>
@@ -16840,7 +19299,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="121" t="s">
         <v>37</v>
       </c>
@@ -16876,7 +19335,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="133" t="s">
         <v>44</v>
       </c>
@@ -16908,7 +19367,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="121"/>
       <c r="B18" s="157"/>
       <c r="C18" s="160"/>
@@ -16928,7 +19387,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="178"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -16944,7 +19403,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="121" t="s">
         <v>59</v>
       </c>
@@ -16980,7 +19439,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="143" t="s">
         <v>200</v>
       </c>
@@ -17008,7 +19467,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="143" t="s">
         <v>199</v>
       </c>
@@ -17037,7 +19496,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="250" t="s">
         <v>117</v>
       </c>
@@ -17065,7 +19524,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="143" t="s">
         <v>126</v>
       </c>
@@ -17091,7 +19550,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="250" t="s">
         <v>197</v>
       </c>
@@ -17112,7 +19571,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="250" t="s">
         <v>198</v>
       </c>
@@ -17134,7 +19593,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="139"/>
       <c r="B27" s="205"/>
       <c r="C27" s="207"/>
@@ -17154,7 +19613,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="251"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -17174,7 +19633,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="251"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -17198,7 +19657,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="166"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -17220,7 +19679,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="205"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -17242,7 +19701,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="157"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -17258,7 +19717,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="165"/>
       <c r="B33" s="165"/>
       <c r="C33" s="165"/>
@@ -17273,7 +19732,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -17288,7 +19747,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -17303,23 +19762,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>
@@ -17338,38 +19797,38 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81B197F3-452B-4BFD-A78F-1734436ED00A}">
   <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="115" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="115" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="115" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="115" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="115" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="115" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" style="115" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="115" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="115" customWidth="1"/>
-    <col min="10" max="10" width="12.36328125" style="115" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="115" customWidth="1"/>
-    <col min="12" max="16384" width="13.90625" style="115"/>
+    <col min="2" max="2" width="12.109375" style="115" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="115" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="115" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="115" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="115" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" style="115" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="115" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="115" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="115" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="115" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="243"/>
       <c r="B1" s="244"/>
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="290" t="s">
+      <c r="F1" s="303" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="290"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
       <c r="K1" s="165"/>
     </row>
-    <row r="2" spans="1:15" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="121" t="s">
         <v>0</v>
       </c>
@@ -17404,7 +19863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="170" t="s">
         <v>196</v>
       </c>
@@ -17439,7 +19898,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="130" t="s">
         <v>195</v>
       </c>
@@ -17464,7 +19923,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="206"/>
       <c r="B5" s="130" t="s">
         <v>21</v>
@@ -17491,7 +19950,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="130"/>
       <c r="B6" s="130" t="s">
         <v>134</v>
@@ -17520,7 +19979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="247" t="s">
         <v>114</v>
       </c>
@@ -17549,7 +20008,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="170" t="s">
         <v>194</v>
       </c>
@@ -17578,7 +20037,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="130" t="s">
         <v>92</v>
       </c>
@@ -17611,7 +20070,7 @@
       </c>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="130" t="s">
         <v>222</v>
       </c>
@@ -17642,7 +20101,7 @@
       </c>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="130"/>
       <c r="B11" s="130" t="s">
         <v>137</v>
@@ -17663,7 +20122,7 @@
       </c>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="248" t="s">
         <v>113</v>
       </c>
@@ -17687,7 +20146,7 @@
       </c>
       <c r="M12" s="122"/>
     </row>
-    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="130" t="s">
         <v>99</v>
       </c>
@@ -17707,7 +20166,7 @@
       </c>
       <c r="M13" s="122"/>
     </row>
-    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="130" t="s">
         <v>82</v>
       </c>
@@ -17733,7 +20192,7 @@
       <c r="N14" s="122"/>
       <c r="O14" s="122"/>
     </row>
-    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="157"/>
       <c r="B15" s="256" t="s">
         <v>219</v>
@@ -17753,7 +20212,7 @@
       <c r="N15" s="122"/>
       <c r="O15" s="122"/>
     </row>
-    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="121" t="s">
         <v>37</v>
       </c>
@@ -17786,7 +20245,7 @@
       <c r="N16" s="122"/>
       <c r="O16" s="122"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="133" t="s">
         <v>44</v>
       </c>
@@ -17818,7 +20277,7 @@
       <c r="N17" s="122"/>
       <c r="O17" s="122"/>
     </row>
-    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="121"/>
       <c r="B18" s="157"/>
       <c r="C18" s="140"/>
@@ -17837,7 +20296,7 @@
       <c r="N18" s="122"/>
       <c r="O18" s="122"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="178"/>
       <c r="B19" s="121"/>
       <c r="C19" s="157"/>
@@ -17853,7 +20312,7 @@
       <c r="N19" s="122"/>
       <c r="O19" s="122"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="121" t="s">
         <v>59</v>
       </c>
@@ -17889,7 +20348,7 @@
       <c r="N20" s="122"/>
       <c r="O20" s="122"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="133" t="s">
         <v>154</v>
       </c>
@@ -17917,7 +20376,7 @@
       <c r="N21" s="122"/>
       <c r="O21" s="122"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="133" t="s">
         <v>153</v>
       </c>
@@ -17946,7 +20405,7 @@
       <c r="N22" s="122"/>
       <c r="O22" s="122"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="263" t="s">
         <v>224</v>
       </c>
@@ -17974,7 +20433,7 @@
       <c r="N23" s="122"/>
       <c r="O23" s="122"/>
     </row>
-    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="133" t="s">
         <v>223</v>
       </c>
@@ -18000,7 +20459,7 @@
       <c r="N24" s="122"/>
       <c r="O24" s="122"/>
     </row>
-    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="262" t="s">
         <v>122</v>
       </c>
@@ -18021,7 +20480,7 @@
       <c r="N25" s="122"/>
       <c r="O25" s="122"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="263" t="s">
         <v>123</v>
       </c>
@@ -18043,7 +20502,7 @@
       <c r="N26" s="122"/>
       <c r="O26" s="122"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="139"/>
       <c r="B27" s="205"/>
       <c r="C27" s="207"/>
@@ -18063,7 +20522,7 @@
       <c r="N27" s="122"/>
       <c r="O27" s="122"/>
     </row>
-    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="251"/>
       <c r="B28" s="157"/>
       <c r="C28" s="193"/>
@@ -18080,7 +20539,7 @@
       <c r="N28" s="122"/>
       <c r="O28" s="122"/>
     </row>
-    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="251"/>
       <c r="B29" s="157"/>
       <c r="C29" s="207"/>
@@ -18104,7 +20563,7 @@
       <c r="N29" s="122"/>
       <c r="O29" s="122"/>
     </row>
-    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="166"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
@@ -18124,7 +20583,7 @@
       <c r="N30" s="122"/>
       <c r="O30" s="122"/>
     </row>
-    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="205"/>
       <c r="B31" s="157"/>
       <c r="C31" s="207"/>
@@ -18144,7 +20603,7 @@
       <c r="N31" s="122"/>
       <c r="O31" s="122"/>
     </row>
-    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="157"/>
       <c r="B32" s="157"/>
       <c r="C32" s="157"/>
@@ -18163,7 +20622,7 @@
       <c r="M32" s="122"/>
       <c r="N32" s="122"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="165"/>
       <c r="B33" s="165"/>
       <c r="C33" s="165"/>
@@ -18180,7 +20639,7 @@
       <c r="M33" s="122"/>
       <c r="N33" s="122"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="122"/>
       <c r="B34" s="122"/>
       <c r="C34" s="122"/>
@@ -18197,7 +20656,7 @@
       <c r="M34" s="122"/>
       <c r="N34" s="122"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="122"/>
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
@@ -18212,23 +20671,23 @@
       <c r="M35" s="122"/>
       <c r="N35" s="122"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M36" s="122"/>
       <c r="N36" s="122"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M37" s="122"/>
       <c r="N37" s="122"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M38" s="122"/>
       <c r="N38" s="122"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M39" s="122"/>
       <c r="N39" s="122"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="M40" s="122"/>
       <c r="N40" s="122"/>
     </row>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0E0E44-26EA-4B0E-8D40-C0AE2F686E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C3C04A-D7D9-41FA-AE6E-17BAF47F54CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="15" sheetId="163" r:id="rId18"/>
     <sheet name="15ауысым" sheetId="164" r:id="rId19"/>
     <sheet name="16" sheetId="165" r:id="rId20"/>
+    <sheet name="17" sheetId="166" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -93,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3498" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3673" uniqueCount="263">
   <si>
     <t>СБ</t>
   </si>
@@ -893,6 +894,12 @@
   </si>
   <si>
     <t xml:space="preserve">16.10.2026 ж </t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.10.2026 ж </t>
+  </si>
+  <si>
+    <t>С13-Н2806/12</t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1512,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="304">
+  <cellXfs count="305">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2331,6 +2338,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2661,10 +2671,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="301" t="s">
+      <c r="F1" s="302" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="302"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -3713,10 +3723,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -4622,10 +4632,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5542,10 +5552,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6456,10 +6466,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7382,10 +7392,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8306,10 +8316,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9225,10 +9235,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10146,10 +10156,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11066,10 +11076,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -11851,10 +11861,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12634,10 +12644,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="301" t="s">
+      <c r="F1" s="302" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="302"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13538,10 +13548,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14284,6 +14294,784 @@
       <c r="J31" s="207" t="s">
         <v>110</v>
       </c>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA06455-634E-4581-B307-35B05882C581}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="304" t="s">
+        <v>261</v>
+      </c>
+      <c r="G1" s="304"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="130" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="133" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="143" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="234"/>
+      <c r="G4" s="133" t="s">
+        <v>243</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="224" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>241</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="288" t="s">
+        <v>186</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="130" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="I8" s="223" t="s">
+        <v>213</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="143" t="s">
+        <v>259</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>252</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="170" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="143" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="234"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="143" t="s">
+        <v>254</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="143" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="143" t="s">
+        <v>255</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="143" t="s">
+        <v>176</v>
+      </c>
+      <c r="K13" s="170" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="151"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="141" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="223" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="234"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="133"/>
+      <c r="K16" s="150"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="133" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="159" t="s">
+        <v>227</v>
+      </c>
+      <c r="J17" s="234"/>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="267" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>250</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="143" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="263" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="133" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23" s="267" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="234"/>
+      <c r="D23" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="267" t="s">
+        <v>251</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>125</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="143" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>232</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="234"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="238" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="250" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="250" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="234"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" s="207" t="s">
+        <v>127</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="139"/>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J27" s="193" t="s">
+        <v>257</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237" t="s">
+        <v>56</v>
+      </c>
+      <c r="J28" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="237"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="207"/>
       <c r="K31" s="140" t="s">
         <v>70</v>
       </c>
@@ -14326,10 +15114,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="301" t="s">
+      <c r="F1" s="302" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="302"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -15240,10 +16028,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="301" t="s">
+      <c r="F1" s="302" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="302"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -16154,10 +16942,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="301" t="s">
+      <c r="F1" s="302" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="302"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -17070,10 +17858,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="301" t="s">
+      <c r="F1" s="302" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="302"/>
+      <c r="G1" s="303"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -17988,10 +18776,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18906,10 +19694,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19819,10 +20607,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="303" t="s">
+      <c r="F1" s="304" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="304"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C3C04A-D7D9-41FA-AE6E-17BAF47F54CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A14F55-A204-4E97-883A-B5DA2AC188CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="15ауысым" sheetId="164" r:id="rId19"/>
     <sheet name="16" sheetId="165" r:id="rId20"/>
     <sheet name="17" sheetId="166" r:id="rId21"/>
+    <sheet name="18" sheetId="167" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -94,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3673" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3847" uniqueCount="270">
   <si>
     <t>СБ</t>
   </si>
@@ -900,6 +901,27 @@
   </si>
   <si>
     <t>С13-Н2806/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.10.2026 ж </t>
+  </si>
+  <si>
+    <t>11-H3406/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С13-648AMY01н </t>
+  </si>
+  <si>
+    <t>С13-H2718/12</t>
+  </si>
+  <si>
+    <t>13-H2808/12н</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 13-Н1074/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13-Н2819/12 </t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1534,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="305">
+  <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2341,6 +2363,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2367,9 +2395,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF99FF"/>
+      <color rgb="FFFF66FF"/>
       <color rgb="FF0F0FF9"/>
       <color rgb="FFFF00FF"/>
-      <color rgb="FFFF66FF"/>
       <color rgb="FF660033"/>
       <color rgb="FF00602B"/>
       <color rgb="FF007635"/>
@@ -2671,10 +2700,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="302" t="s">
+      <c r="F1" s="304" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="305"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -3723,10 +3752,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -4632,10 +4661,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5552,10 +5581,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6466,10 +6495,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7392,10 +7421,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8316,10 +8345,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9235,10 +9264,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10156,10 +10185,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11076,10 +11105,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -11861,10 +11890,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12644,10 +12673,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="302" t="s">
+      <c r="F1" s="304" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="305"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13548,10 +13577,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14326,10 +14355,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15071,6 +15100,782 @@
       <c r="G31" s="234"/>
       <c r="H31" s="178"/>
       <c r="I31" s="237"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C34F42F-F97D-424E-A1CE-7600D455C228}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="302"/>
+      <c r="F1" s="306" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1" s="306"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="256" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="133" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="234"/>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="130" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="303" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="130" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="303" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="267" t="s">
+        <v>259</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>252</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="256" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="234"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="267" t="s">
+        <v>254</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="267" t="s">
+        <v>255</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="256" t="s">
+        <v>265</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="267" t="s">
+        <v>176</v>
+      </c>
+      <c r="K13" s="256" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130"/>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="151"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="141" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="267" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="234"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="133"/>
+      <c r="K16" s="150"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="133" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="159"/>
+      <c r="J17" s="234"/>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="267" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>250</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="250" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="267" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="267" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="234"/>
+      <c r="D23" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="267" t="s">
+        <v>251</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>125</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="267" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>232</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="234"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="238" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="250" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="250" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="234"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="139"/>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J27" s="207" t="s">
+        <v>120</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237" t="s">
+        <v>56</v>
+      </c>
+      <c r="J28" s="207" t="s">
+        <v>81</v>
+      </c>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237" t="s">
+        <v>257</v>
+      </c>
+      <c r="J29" s="207" t="s">
+        <v>210</v>
+      </c>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="237" t="s">
+        <v>268</v>
+      </c>
+      <c r="J30" s="207"/>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237" t="s">
+        <v>269</v>
+      </c>
       <c r="J31" s="207"/>
       <c r="K31" s="140" t="s">
         <v>70</v>
@@ -15114,10 +15919,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="302" t="s">
+      <c r="F1" s="304" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="305"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -16028,10 +16833,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="302" t="s">
+      <c r="F1" s="304" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="305"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -16942,10 +17747,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="302" t="s">
+      <c r="F1" s="304" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="305"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -17858,10 +18663,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="302" t="s">
+      <c r="F1" s="304" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="303"/>
+      <c r="G1" s="305"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -18776,10 +19581,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19694,10 +20499,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20607,10 +21412,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="306" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="304"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A14F55-A204-4E97-883A-B5DA2AC188CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B56042-66C0-4D9E-BFE4-C9090EADBA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="16" sheetId="165" r:id="rId20"/>
     <sheet name="17" sheetId="166" r:id="rId21"/>
     <sheet name="18" sheetId="167" r:id="rId22"/>
+    <sheet name="19" sheetId="168" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -95,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3847" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4021" uniqueCount="274">
   <si>
     <t>СБ</t>
   </si>
@@ -922,6 +923,18 @@
   </si>
   <si>
     <t xml:space="preserve">13-Н2819/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.10.2026 ж </t>
+  </si>
+  <si>
+    <t>13-H2807/12н</t>
+  </si>
+  <si>
+    <t>С13-H2808/12</t>
+  </si>
+  <si>
+    <t>13-H2642/12</t>
   </si>
 </sst>
 </file>
@@ -1534,7 +1547,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="307">
+  <cellXfs count="308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2369,6 +2382,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2700,10 +2716,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="305" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="305"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -3752,10 +3768,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -4661,10 +4677,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5581,10 +5597,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6495,10 +6511,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7421,10 +7437,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8345,10 +8361,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9264,10 +9280,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10185,10 +10201,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11105,10 +11121,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -11890,10 +11906,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12673,10 +12689,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="305" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="305"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13577,10 +13593,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14355,10 +14371,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15133,10 +15149,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15876,6 +15892,782 @@
       <c r="I31" s="237" t="s">
         <v>269</v>
       </c>
+      <c r="J31" s="207"/>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382E376F-388A-4B6E-BBF7-5E436B5B7BEE}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="304"/>
+      <c r="F1" s="307" t="s">
+        <v>270</v>
+      </c>
+      <c r="G1" s="307"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="256" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="133" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="234"/>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="138" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="303" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="130" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="303" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="267" t="s">
+        <v>259</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>252</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="256" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="234"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="267" t="s">
+        <v>254</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="267" t="s">
+        <v>255</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="256" t="s">
+        <v>265</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="267" t="s">
+        <v>176</v>
+      </c>
+      <c r="K13" s="256" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="151"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="141" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="234"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="133"/>
+      <c r="K16" s="150"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="133" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="159"/>
+      <c r="J17" s="234"/>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="267" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>250</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="250" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="267" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="267" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="234"/>
+      <c r="C23" s="234"/>
+      <c r="D23" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="267" t="s">
+        <v>251</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="267" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>232</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="234"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="250" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>55</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="250" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="234"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J26" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="250" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237" t="s">
+        <v>56</v>
+      </c>
+      <c r="J27" s="207" t="s">
+        <v>273</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237" t="s">
+        <v>268</v>
+      </c>
+      <c r="J28" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237" t="s">
+        <v>186</v>
+      </c>
+      <c r="J29" s="207"/>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="138"/>
       <c r="J31" s="207"/>
       <c r="K31" s="140" t="s">
         <v>70</v>
@@ -15919,10 +16711,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="305" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="305"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -16833,10 +17625,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="305" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="305"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -17747,10 +18539,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="305" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="305"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -18663,10 +19455,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="304" t="s">
+      <c r="F1" s="305" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="305"/>
+      <c r="G1" s="306"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -19581,10 +20373,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20499,10 +21291,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21412,10 +22204,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="306" t="s">
+      <c r="F1" s="307" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B56042-66C0-4D9E-BFE4-C9090EADBA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592AD190-F732-4BB1-9992-B4CF41812ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="17" sheetId="166" r:id="rId21"/>
     <sheet name="18" sheetId="167" r:id="rId22"/>
     <sheet name="19" sheetId="168" r:id="rId23"/>
+    <sheet name="20" sheetId="169" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -96,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4021" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4195" uniqueCount="279">
   <si>
     <t>СБ</t>
   </si>
@@ -935,6 +936,21 @@
   </si>
   <si>
     <t>13-H2642/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.10.2026 ж </t>
+  </si>
+  <si>
+    <t xml:space="preserve">С12-Н798399/12 </t>
+  </si>
+  <si>
+    <t>С13-Н3641/12</t>
+  </si>
+  <si>
+    <t>13-H1293/12</t>
+  </si>
+  <si>
+    <t>13-H2663/12</t>
   </si>
 </sst>
 </file>
@@ -1547,7 +1563,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="310">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2385,6 +2401,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="16" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2411,9 +2433,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0F0FF9"/>
       <color rgb="FFFF99FF"/>
       <color rgb="FFFF66FF"/>
-      <color rgb="FF0F0FF9"/>
       <color rgb="FFFF00FF"/>
       <color rgb="FF660033"/>
       <color rgb="FF00602B"/>
@@ -2716,10 +2738,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="305" t="s">
+      <c r="F1" s="307" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="308"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -3768,10 +3790,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -4677,10 +4699,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5597,10 +5619,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6511,10 +6533,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7437,10 +7459,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8361,10 +8383,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9280,10 +9302,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10201,10 +10223,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11121,10 +11143,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -11906,10 +11928,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12689,10 +12711,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="305" t="s">
+      <c r="F1" s="307" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="308"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13593,10 +13615,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14371,10 +14393,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15149,10 +15171,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15925,10 +15947,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16363,8 +16385,8 @@
       <c r="D17" s="133" t="s">
         <v>146</v>
       </c>
-      <c r="E17" s="133" t="s">
-        <v>142</v>
+      <c r="E17" s="151" t="s">
+        <v>275</v>
       </c>
       <c r="F17" s="150" t="s">
         <v>46</v>
@@ -16668,6 +16690,782 @@
       <c r="G31" s="234"/>
       <c r="H31" s="178"/>
       <c r="I31" s="138"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4DD20DC-DA73-4767-9875-CD4DD7E01E00}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="305"/>
+      <c r="F1" s="309" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1" s="309"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="256" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="234"/>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="130" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="267" t="s">
+        <v>259</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>252</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="256" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="133"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="267" t="s">
+        <v>254</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="267" t="s">
+        <v>255</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="256" t="s">
+        <v>265</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="267" t="s">
+        <v>176</v>
+      </c>
+      <c r="K13" s="256" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="151"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="141" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" s="234"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="133"/>
+      <c r="K16" s="150"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="159"/>
+      <c r="J17" s="234"/>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="267" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>250</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="133" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="250" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="267" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="267" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="234"/>
+      <c r="C23" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="267" t="s">
+        <v>251</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="267" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>232</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="234"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="250" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>55</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="250" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="234"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J26" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="250" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237" t="s">
+        <v>54</v>
+      </c>
+      <c r="J27" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237" t="s">
+        <v>268</v>
+      </c>
+      <c r="J28" s="207"/>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237" t="s">
+        <v>186</v>
+      </c>
+      <c r="J29" s="207"/>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="J30" s="207"/>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237" t="s">
+        <v>278</v>
+      </c>
       <c r="J31" s="207"/>
       <c r="K31" s="140" t="s">
         <v>70</v>
@@ -16711,10 +17509,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="305" t="s">
+      <c r="F1" s="307" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="308"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -17625,10 +18423,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="305" t="s">
+      <c r="F1" s="307" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="308"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -18539,10 +19337,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="305" t="s">
+      <c r="F1" s="307" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="308"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -19455,10 +20253,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="305" t="s">
+      <c r="F1" s="307" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="306"/>
+      <c r="G1" s="308"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -20373,10 +21171,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21291,10 +22089,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -22204,10 +23002,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="309" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="307"/>
+      <c r="G1" s="309"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592AD190-F732-4BB1-9992-B4CF41812ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E051E5EF-8D38-4099-A5C7-AC32A2E55B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" firstSheet="1" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -32,6 +32,8 @@
     <sheet name="18" sheetId="167" r:id="rId22"/>
     <sheet name="19" sheetId="168" r:id="rId23"/>
     <sheet name="20" sheetId="169" r:id="rId24"/>
+    <sheet name="20 түскі ауысым" sheetId="170" r:id="rId25"/>
+    <sheet name="21" sheetId="171" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -97,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4195" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4545" uniqueCount="287">
   <si>
     <t>СБ</t>
   </si>
@@ -951,6 +953,30 @@
   </si>
   <si>
     <t>13-H2663/12</t>
+  </si>
+  <si>
+    <t>34-Н2797/12н</t>
+  </si>
+  <si>
+    <t>34-Н2869/12</t>
+  </si>
+  <si>
+    <t>36-H3206/12н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34-Н2893/12 </t>
+  </si>
+  <si>
+    <t>34-Н3164/12 д/н</t>
+  </si>
+  <si>
+    <t>34-Н3400/12д</t>
+  </si>
+  <si>
+    <t>34-Н3400/12н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.10.2026 ж </t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1154,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1174,6 +1200,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF00FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1563,7 +1595,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="310">
+  <cellXfs count="313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2407,6 +2439,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="16" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2433,8 +2474,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF99FF"/>
       <color rgb="FF0F0FF9"/>
-      <color rgb="FFFF99FF"/>
       <color rgb="FFFF66FF"/>
       <color rgb="FFFF00FF"/>
       <color rgb="FF660033"/>
@@ -2738,10 +2779,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="310" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="308"/>
+      <c r="G1" s="311"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -3790,10 +3831,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -4699,10 +4740,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5619,10 +5660,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6533,10 +6574,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7459,10 +7500,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8383,10 +8424,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9302,10 +9343,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10223,10 +10264,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11143,10 +11184,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -11928,10 +11969,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12711,10 +12752,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="310" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="308"/>
+      <c r="G1" s="311"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13615,10 +13656,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14393,10 +14434,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15171,10 +15212,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15947,10 +15988,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16723,10 +16764,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17481,6 +17522,1561 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAACE2F4-4E27-4C9F-86BC-086C18ABD0D7}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="307"/>
+      <c r="F1" s="312" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1" s="312"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="256" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="234"/>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="130" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="267" t="s">
+        <v>281</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>282</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="256" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="133"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="308" t="s">
+        <v>284</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="267" t="s">
+        <v>283</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="256" t="s">
+        <v>265</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="267" t="s">
+        <v>231</v>
+      </c>
+      <c r="K13" s="256" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="151"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="267" t="s">
+        <v>279</v>
+      </c>
+      <c r="K14" s="267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="141" t="s">
+        <v>171</v>
+      </c>
+      <c r="K15" s="234"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" s="150"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="234"/>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="267" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="267" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="250" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="308" t="s">
+        <v>285</v>
+      </c>
+      <c r="C22" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>208</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="267" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="234"/>
+      <c r="C23" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="267" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="234"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="250" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>55</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="250" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="234"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J26" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="250" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237" t="s">
+        <v>54</v>
+      </c>
+      <c r="J27" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237" t="s">
+        <v>268</v>
+      </c>
+      <c r="J28" s="207"/>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237" t="s">
+        <v>186</v>
+      </c>
+      <c r="J29" s="207"/>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="J30" s="207"/>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E974D070-6278-4D95-9DFE-F5693FD104B5}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="309"/>
+      <c r="F1" s="312" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1" s="312"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="256" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="234"/>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="130" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="267" t="s">
+        <v>281</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>282</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="256" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="133"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="308" t="s">
+        <v>284</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="267" t="s">
+        <v>283</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="256" t="s">
+        <v>265</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="267" t="s">
+        <v>231</v>
+      </c>
+      <c r="K13" s="256" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="151"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="267" t="s">
+        <v>279</v>
+      </c>
+      <c r="K14" s="267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="141" t="s">
+        <v>171</v>
+      </c>
+      <c r="K15" s="234"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" s="150"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="234"/>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="267" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="267" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="250" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>208</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="267" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="308" t="s">
+        <v>285</v>
+      </c>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="267" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="234"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="250" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="250" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="234"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>54</v>
+      </c>
+      <c r="J26" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="250" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237" t="s">
+        <v>268</v>
+      </c>
+      <c r="J27" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237" t="s">
+        <v>186</v>
+      </c>
+      <c r="J28" s="207" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="J29" s="207"/>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="237"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -17509,10 +19105,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="310" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="308"/>
+      <c r="G1" s="311"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -18423,10 +20019,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="310" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="308"/>
+      <c r="G1" s="311"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -19337,10 +20933,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="310" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="308"/>
+      <c r="G1" s="311"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -20253,10 +21849,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="307" t="s">
+      <c r="F1" s="310" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="308"/>
+      <c r="G1" s="311"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -21171,10 +22767,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -22089,10 +23685,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -23002,10 +24598,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="309" t="s">
+      <c r="F1" s="312" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="309"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E051E5EF-8D38-4099-A5C7-AC32A2E55B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87C8BD9-9B2D-4677-9BBB-592A84EC3653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" firstSheet="1" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" firstSheet="2" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <sheet name="20" sheetId="169" r:id="rId24"/>
     <sheet name="20 түскі ауысым" sheetId="170" r:id="rId25"/>
     <sheet name="21" sheetId="171" r:id="rId26"/>
+    <sheet name="22" sheetId="172" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -99,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4545" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4720" uniqueCount="290">
   <si>
     <t>СБ</t>
   </si>
@@ -977,6 +978,15 @@
   </si>
   <si>
     <t xml:space="preserve">21.10.2026 ж </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.10.2026 ж </t>
+  </si>
+  <si>
+    <t>С13-H2648/12н</t>
+  </si>
+  <si>
+    <t>34-Н2893/12 д/н</t>
   </si>
 </sst>
 </file>
@@ -1595,7 +1605,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="313">
+  <cellXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2445,6 +2455,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2779,10 +2792,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="310" t="s">
+      <c r="F1" s="311" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="311"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -3831,10 +3844,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -4740,10 +4753,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5660,10 +5673,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6574,10 +6587,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7500,10 +7513,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8424,10 +8437,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9343,10 +9356,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10264,10 +10277,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11184,10 +11197,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -11969,10 +11982,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12752,10 +12765,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="310" t="s">
+      <c r="F1" s="311" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="311"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13656,10 +13669,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14434,10 +14447,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15212,10 +15225,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15988,10 +16001,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16764,10 +16777,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17540,10 +17553,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18318,10 +18331,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19077,6 +19090,784 @@
     <mergeCell ref="F1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC3E9D27-A367-41A8-AC3F-0B16D45C9E47}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="310"/>
+      <c r="F1" s="313" t="s">
+        <v>287</v>
+      </c>
+      <c r="G1" s="313"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="256" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="234"/>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="130" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="267" t="s">
+        <v>281</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="267" t="s">
+        <v>289</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="256" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="133"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="308" t="s">
+        <v>284</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="256" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="267" t="s">
+        <v>231</v>
+      </c>
+      <c r="K13" s="256" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="267" t="s">
+        <v>279</v>
+      </c>
+      <c r="K14" s="267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="141" t="s">
+        <v>171</v>
+      </c>
+      <c r="K15" s="234"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" s="150"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="234"/>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="267" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="267" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="250" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>208</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="267" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="308" t="s">
+        <v>285</v>
+      </c>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="267" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="234"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="250" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="250" t="s">
+        <v>198</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="234"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>54</v>
+      </c>
+      <c r="J26" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="250" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237" t="s">
+        <v>268</v>
+      </c>
+      <c r="J27" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237" t="s">
+        <v>186</v>
+      </c>
+      <c r="J28" s="207" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="J29" s="207"/>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="237"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19105,10 +19896,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="310" t="s">
+      <c r="F1" s="311" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="311"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -20019,10 +20810,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="310" t="s">
+      <c r="F1" s="311" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="311"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -20933,10 +21724,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="310" t="s">
+      <c r="F1" s="311" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="311"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -21849,10 +22640,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="310" t="s">
+      <c r="F1" s="311" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="311"/>
+      <c r="G1" s="312"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22767,10 +23558,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -23685,10 +24476,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -24598,10 +25389,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87C8BD9-9B2D-4677-9BBB-592A84EC3653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D18F37-999B-41A5-8977-9163A9330E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" firstSheet="2" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" firstSheet="3" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="20 түскі ауысым" sheetId="170" r:id="rId25"/>
     <sheet name="21" sheetId="171" r:id="rId26"/>
     <sheet name="22" sheetId="172" r:id="rId27"/>
+    <sheet name="22-2" sheetId="173" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -100,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4720" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4896" uniqueCount="292">
   <si>
     <t>СБ</t>
   </si>
@@ -987,6 +988,12 @@
   </si>
   <si>
     <t>34-Н2893/12 д/н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.10.2026 ж </t>
+  </si>
+  <si>
+    <t>34-Н2795/12н</t>
   </si>
 </sst>
 </file>
@@ -1605,7 +1612,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="314">
+  <cellXfs count="315">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2455,6 +2462,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2792,10 +2802,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="311" t="s">
+      <c r="F1" s="312" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -3844,10 +3854,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -4753,10 +4763,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5673,10 +5683,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6587,10 +6597,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7513,10 +7523,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8437,10 +8447,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9356,10 +9366,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10277,10 +10287,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11197,10 +11207,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -11982,10 +11992,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12765,10 +12775,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="311" t="s">
+      <c r="F1" s="312" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13669,10 +13679,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14447,10 +14457,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15225,10 +15235,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16001,10 +16011,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16777,10 +16787,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17553,10 +17563,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18331,10 +18341,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19108,10 +19118,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="310"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19823,6 +19833,786 @@
       <c r="I29" s="237" t="s">
         <v>277</v>
       </c>
+      <c r="J29" s="207"/>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="237"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52DD090C-3418-4B12-981D-D19F38FBCFEF}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="311"/>
+      <c r="F1" s="314" t="s">
+        <v>290</v>
+      </c>
+      <c r="G1" s="314"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="256" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="234"/>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="256" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="267" t="s">
+        <v>281</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="130" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="133"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="K10" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="133" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="308" t="s">
+        <v>284</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="256" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="267" t="s">
+        <v>291</v>
+      </c>
+      <c r="K13" s="256" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="267" t="s">
+        <v>231</v>
+      </c>
+      <c r="K14" s="267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="267" t="s">
+        <v>279</v>
+      </c>
+      <c r="K15" s="234"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="141" t="s">
+        <v>171</v>
+      </c>
+      <c r="K16" s="150"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="250" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="267" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="250" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>208</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="267" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="308" t="s">
+        <v>285</v>
+      </c>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="250" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="130"/>
+      <c r="I24" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="267" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>54</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="267" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="234"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>268</v>
+      </c>
+      <c r="J26" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="250" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237" t="s">
+        <v>186</v>
+      </c>
+      <c r="J27" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="J28" s="207" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237"/>
       <c r="J29" s="207"/>
       <c r="K29" s="140" t="s">
         <v>88</v>
@@ -19896,10 +20686,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="311" t="s">
+      <c r="F1" s="312" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -20810,10 +21600,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="311" t="s">
+      <c r="F1" s="312" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -21724,10 +22514,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="311" t="s">
+      <c r="F1" s="312" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22640,10 +23430,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="311" t="s">
+      <c r="F1" s="312" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="312"/>
+      <c r="G1" s="313"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -23558,10 +24348,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -24476,10 +25266,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -25389,10 +26179,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D18F37-999B-41A5-8977-9163A9330E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B20EE4-E2D1-4561-8223-74CCD055F9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" firstSheet="3" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" firstSheet="4" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -36,6 +36,7 @@
     <sheet name="21" sheetId="171" r:id="rId26"/>
     <sheet name="22" sheetId="172" r:id="rId27"/>
     <sheet name="22-2" sheetId="173" r:id="rId28"/>
+    <sheet name="23" sheetId="174" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -101,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4896" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5073" uniqueCount="295">
   <si>
     <t>СБ</t>
   </si>
@@ -994,6 +995,15 @@
   </si>
   <si>
     <t>34-Н2795/12н</t>
+  </si>
+  <si>
+    <t>34-Н3391/12д</t>
+  </si>
+  <si>
+    <t>34-Н3160/12д</t>
+  </si>
+  <si>
+    <t>36-H3206/12д/н</t>
   </si>
 </sst>
 </file>
@@ -1612,7 +1622,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="315">
+  <cellXfs count="316">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2473,6 +2483,9 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2802,10 +2815,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -3854,10 +3867,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -4763,10 +4776,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5683,10 +5696,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6597,10 +6610,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7523,10 +7536,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8447,10 +8460,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9366,10 +9379,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10287,10 +10300,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11207,10 +11220,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -11992,10 +12005,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12775,10 +12788,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13679,10 +13692,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14457,10 +14470,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15235,10 +15248,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16011,10 +16024,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16787,10 +16800,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17563,10 +17576,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18341,10 +18354,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19118,10 +19131,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="310"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19896,10 +19909,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="311"/>
-      <c r="F1" s="314" t="s">
-        <v>290</v>
-      </c>
-      <c r="G1" s="314"/>
+      <c r="F1" s="315" t="s">
+        <v>287</v>
+      </c>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20046,8 +20059,8 @@
       </c>
       <c r="E6" s="138"/>
       <c r="F6" s="130"/>
-      <c r="G6" s="130" t="s">
-        <v>272</v>
+      <c r="G6" s="133" t="s">
+        <v>78</v>
       </c>
       <c r="H6" s="141" t="s">
         <v>80</v>
@@ -20084,7 +20097,7 @@
       <c r="I7" s="150" t="s">
         <v>66</v>
       </c>
-      <c r="J7" s="133" t="s">
+      <c r="J7" s="303" t="s">
         <v>187</v>
       </c>
       <c r="K7" s="138" t="s">
@@ -20149,7 +20162,7 @@
       <c r="I9" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="133" t="s">
+      <c r="J9" s="303" t="s">
         <v>182</v>
       </c>
       <c r="K9" s="151" t="s">
@@ -20178,7 +20191,9 @@
       </c>
       <c r="G10" s="133"/>
       <c r="H10" s="234"/>
-      <c r="I10" s="133"/>
+      <c r="I10" s="133" t="s">
+        <v>54</v>
+      </c>
       <c r="J10" s="133" t="s">
         <v>173</v>
       </c>
@@ -20286,7 +20301,9 @@
       <c r="J15" s="267" t="s">
         <v>279</v>
       </c>
-      <c r="K15" s="234"/>
+      <c r="K15" s="308" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="121" t="s">
@@ -20366,7 +20383,7 @@
       <c r="G18" s="157"/>
       <c r="H18" s="306"/>
       <c r="I18" s="157"/>
-      <c r="J18" s="140"/>
+      <c r="J18" s="237"/>
       <c r="K18" s="234"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -20506,12 +20523,12 @@
       </c>
       <c r="B24" s="234"/>
       <c r="C24" s="234"/>
-      <c r="D24" s="267" t="s">
+      <c r="D24" s="308" t="s">
         <v>178</v>
       </c>
       <c r="E24" s="234"/>
       <c r="F24" s="234"/>
-      <c r="G24" s="237" t="s">
+      <c r="G24" s="133" t="s">
         <v>136</v>
       </c>
       <c r="H24" s="130"/>
@@ -20535,10 +20552,10 @@
       <c r="G25" s="139"/>
       <c r="H25" s="178"/>
       <c r="I25" s="237" t="s">
-        <v>54</v>
+        <v>268</v>
       </c>
       <c r="J25" s="207" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="K25" s="193"/>
     </row>
@@ -20556,10 +20573,10 @@
       <c r="G26" s="130"/>
       <c r="H26" s="238"/>
       <c r="I26" s="237" t="s">
-        <v>268</v>
+        <v>186</v>
       </c>
       <c r="J26" s="207" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="K26" s="193"/>
     </row>
@@ -20575,10 +20592,10 @@
       <c r="G27" s="133"/>
       <c r="H27" s="234"/>
       <c r="I27" s="237" t="s">
-        <v>186</v>
+        <v>277</v>
       </c>
       <c r="J27" s="207" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="K27" s="193"/>
     </row>
@@ -20591,12 +20608,8 @@
       <c r="F28" s="166"/>
       <c r="G28" s="16"/>
       <c r="H28" s="234"/>
-      <c r="I28" s="237" t="s">
-        <v>277</v>
-      </c>
-      <c r="J28" s="207" t="s">
-        <v>135</v>
-      </c>
+      <c r="I28" s="237"/>
+      <c r="J28" s="207"/>
       <c r="K28" s="241" t="s">
         <v>65</v>
       </c>
@@ -20658,6 +20671,787 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1E2066-E0FF-4BA1-A925-09BB04D7807D}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="312"/>
+      <c r="F1" s="315" t="s">
+        <v>290</v>
+      </c>
+      <c r="G1" s="315"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="256" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="141" t="s">
+        <v>208</v>
+      </c>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="303" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="256" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="267" t="s">
+        <v>294</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="303" t="s">
+        <v>182</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="130" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="H10" s="234"/>
+      <c r="I10" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="K10" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="234"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="133" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="308" t="s">
+        <v>284</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="256" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="267" t="s">
+        <v>291</v>
+      </c>
+      <c r="K13" s="256" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="308" t="s">
+        <v>231</v>
+      </c>
+      <c r="K14" s="267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="267" t="s">
+        <v>279</v>
+      </c>
+      <c r="K15" s="308" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="141" t="s">
+        <v>171</v>
+      </c>
+      <c r="K16" s="150"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="250" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="E21" s="255" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="267" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="250" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="139"/>
+      <c r="D22" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="267" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="308" t="s">
+        <v>285</v>
+      </c>
+      <c r="C23" s="133"/>
+      <c r="D23" s="303" t="s">
+        <v>293</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="238" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="250" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="308" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="133" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="130"/>
+      <c r="I24" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="267" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>268</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="267" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="234"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>186</v>
+      </c>
+      <c r="J26" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="250" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="J27" s="207" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237"/>
+      <c r="J28" s="207"/>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237"/>
+      <c r="J29" s="207"/>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="237"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -20686,10 +21480,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -21600,10 +22394,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22514,10 +23308,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -23430,10 +24224,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="312" t="s">
+      <c r="F1" s="313" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="313"/>
+      <c r="G1" s="314"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -24348,10 +25142,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -25266,10 +26060,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -26179,10 +26973,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B20EE4-E2D1-4561-8223-74CCD055F9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF01BAF-8773-4067-9FED-56E6578093FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" firstSheet="4" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" firstSheet="5" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="22" sheetId="172" r:id="rId27"/>
     <sheet name="22-2" sheetId="173" r:id="rId28"/>
     <sheet name="23" sheetId="174" r:id="rId29"/>
+    <sheet name="24" sheetId="175" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -101,8 +102,43 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{616C5DB5-8894-44AF-AA52-577AD995E6EB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+8 702 489 68 89
+Мирас</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5073" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5249" uniqueCount="297">
   <si>
     <t>СБ</t>
   </si>
@@ -1005,6 +1041,12 @@
   <si>
     <t>36-H3206/12д/н</t>
   </si>
+  <si>
+    <t xml:space="preserve">24.10.2026 ж </t>
+  </si>
+  <si>
+    <t>34-Н3391/12д/н</t>
+  </si>
 </sst>
 </file>
 
@@ -1013,7 +1055,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1179,6 +1221,19 @@
       <name val="Tahoma"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1622,7 +1677,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="316">
+  <cellXfs count="317">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2486,6 +2541,9 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2815,10 +2873,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -3867,10 +3925,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -4776,10 +4834,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5696,10 +5754,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6610,10 +6668,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7536,10 +7594,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8460,10 +8518,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9379,10 +9437,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10300,10 +10358,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11220,10 +11278,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12005,10 +12063,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12788,10 +12846,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13692,10 +13750,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14470,10 +14528,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15248,10 +15306,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16024,10 +16082,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16800,10 +16858,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17576,10 +17634,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18354,10 +18412,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19131,10 +19189,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="310"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19909,10 +19967,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="311"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20689,10 +20747,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="312"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>290</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21480,10 +21538,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22366,6 +22424,787 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2310D3F3-43EA-4177-9812-C1AEBA104FB2}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="313"/>
+      <c r="F1" s="316" t="s">
+        <v>295</v>
+      </c>
+      <c r="G1" s="316"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="256" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130" t="s">
+        <v>272</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="256" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="267" t="s">
+        <v>294</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="130" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="250" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="I10" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="K10" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="133" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="308" t="s">
+        <v>284</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="256" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="267" t="s">
+        <v>291</v>
+      </c>
+      <c r="K13" s="256" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="308" t="s">
+        <v>231</v>
+      </c>
+      <c r="K14" s="267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="267" t="s">
+        <v>279</v>
+      </c>
+      <c r="K15" s="133" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="141" t="s">
+        <v>171</v>
+      </c>
+      <c r="K16" s="150"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="250" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="E21" s="141" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="267" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="250" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="139"/>
+      <c r="D22" s="303" t="s">
+        <v>293</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="267" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="308" t="s">
+        <v>285</v>
+      </c>
+      <c r="C23" s="133"/>
+      <c r="D23" s="267" t="s">
+        <v>296</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="250" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="234"/>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="133" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="130"/>
+      <c r="I24" s="237" t="s">
+        <v>268</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="267" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>186</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="267" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="205"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="J26" s="207" t="s">
+        <v>110</v>
+      </c>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="250" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237"/>
+      <c r="J27" s="207" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237"/>
+      <c r="J28" s="207" t="s">
+        <v>52</v>
+      </c>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237"/>
+      <c r="J29" s="207"/>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="237"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -22394,10 +23233,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -23308,10 +24147,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -24224,10 +25063,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="313" t="s">
+      <c r="F1" s="314" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="314"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25142,10 +25981,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -26060,10 +26899,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -26973,10 +27812,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="316" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF01BAF-8773-4067-9FED-56E6578093FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F626A9-EE9B-47A9-AE38-3CB40E7E962E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" firstSheet="5" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" firstSheet="6" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -38,6 +38,7 @@
     <sheet name="22-2" sheetId="173" r:id="rId28"/>
     <sheet name="23" sheetId="174" r:id="rId29"/>
     <sheet name="24" sheetId="175" r:id="rId30"/>
+    <sheet name="25" sheetId="176" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -138,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5249" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5424" uniqueCount="298">
   <si>
     <t>СБ</t>
   </si>
@@ -1046,6 +1047,9 @@
   </si>
   <si>
     <t>34-Н3391/12д/н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.10.2026 ж </t>
   </si>
 </sst>
 </file>
@@ -1677,7 +1681,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="317">
+  <cellXfs count="318">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2544,6 +2548,9 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2873,10 +2880,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -3925,10 +3932,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -4834,10 +4841,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5754,10 +5761,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6668,10 +6675,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7594,10 +7601,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8518,10 +8525,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9437,10 +9444,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10358,10 +10365,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11278,10 +11285,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12063,10 +12070,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12846,10 +12853,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13750,10 +13757,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14528,10 +14535,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15306,10 +15313,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16082,10 +16089,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16858,10 +16865,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17634,10 +17641,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18412,10 +18419,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19189,10 +19196,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="310"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19967,10 +19974,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="311"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20747,10 +20754,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="312"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>290</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21538,10 +21545,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22442,10 +22449,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="313"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>295</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -23205,6 +23212,784 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F6BA9DB-8ABE-430B-9151-6C4973B7C7AB}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="11" width="11.77734375" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.88671875" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133"/>
+      <c r="B1" s="244"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="314"/>
+      <c r="F1" s="317" t="s">
+        <v>297</v>
+      </c>
+      <c r="G1" s="317"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="165"/>
+    </row>
+    <row r="2" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="256" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="150" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="130" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="130"/>
+      <c r="B6" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="138" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="247" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="138" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="256" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="150" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="130" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="267" t="s">
+        <v>294</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="K9" s="151" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="130" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="133" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" s="193"/>
+      <c r="I10" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="K10" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="133" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="150" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="248" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="308" t="s">
+        <v>284</v>
+      </c>
+      <c r="K12" s="150" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="256" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="267" t="s">
+        <v>291</v>
+      </c>
+      <c r="K13" s="256" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="267" t="s">
+        <v>231</v>
+      </c>
+      <c r="K14" s="267" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="157"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="267" t="s">
+        <v>279</v>
+      </c>
+      <c r="K15" s="133" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="141" t="s">
+        <v>171</v>
+      </c>
+      <c r="K16" s="133" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="234"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="121"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="234"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="178"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="157"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="166"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="178"/>
+      <c r="I20" s="238" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="239" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="239" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="250" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="E21" s="141" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="267" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="178"/>
+      <c r="I21" s="238" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="207" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="207"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="250" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="139"/>
+      <c r="D22" s="267" t="s">
+        <v>296</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="178"/>
+      <c r="I22" s="237" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="207"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="267" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="308" t="s">
+        <v>285</v>
+      </c>
+      <c r="C23" s="133"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H23" s="178"/>
+      <c r="I23" s="237" t="s">
+        <v>63</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="193"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="250" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="234"/>
+      <c r="C24" s="234"/>
+      <c r="D24" s="205"/>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="133" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="130"/>
+      <c r="I24" s="237" t="s">
+        <v>268</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="207"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="267" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="237" t="s">
+        <v>186</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K25" s="193"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="267" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="205"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="238"/>
+      <c r="I26" s="237" t="s">
+        <v>277</v>
+      </c>
+      <c r="J26" s="207"/>
+      <c r="K26" s="193"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="250" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="234"/>
+      <c r="I27" s="237" t="s">
+        <v>55</v>
+      </c>
+      <c r="J27" s="207"/>
+      <c r="K27" s="193"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="251"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="234"/>
+      <c r="I28" s="237" t="s">
+        <v>52</v>
+      </c>
+      <c r="J28" s="207"/>
+      <c r="K28" s="241" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="251"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="237"/>
+      <c r="J29" s="207"/>
+      <c r="K29" s="140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="166"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="237"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="166" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="205"/>
+      <c r="B31" s="157"/>
+      <c r="C31" s="207"/>
+      <c r="D31" s="157"/>
+      <c r="E31" s="166"/>
+      <c r="F31" s="160"/>
+      <c r="G31" s="234"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="237"/>
+      <c r="J31" s="207"/>
+      <c r="K31" s="140" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -23233,10 +24018,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -24147,10 +24932,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25063,10 +25848,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="314" t="s">
+      <c r="F1" s="315" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="315"/>
+      <c r="G1" s="316"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25981,10 +26766,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -26899,10 +27684,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -27812,10 +28597,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="316" t="s">
+      <c r="F1" s="317" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="317"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D744B4-87E4-4558-8854-A8CFC2394B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7828976D-0AF0-4970-842C-432CF9BAB072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="13" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5598" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5597" uniqueCount="302">
   <si>
     <t>СБ</t>
   </si>
@@ -1789,7 +1789,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2659,15 +2659,6 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="3" fillId="3" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2681,9 +2672,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2749,6 +2737,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="15" fillId="3" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3071,10 +3080,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="345" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="346"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -4123,10 +4132,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5032,10 +5041,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5952,10 +5961,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6866,10 +6875,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7792,10 +7801,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8716,10 +8725,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9635,10 +9644,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10556,10 +10565,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11476,10 +11485,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12261,10 +12270,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -13044,10 +13053,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="345" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="346"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13948,10 +13957,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14726,10 +14735,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15504,10 +15513,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16280,10 +16289,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17056,10 +17065,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17832,10 +17841,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18610,10 +18619,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19387,10 +19396,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="310"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20165,10 +20174,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="311"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20945,10 +20954,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="312"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>290</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21736,10 +21745,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="345" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="346"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22640,10 +22649,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="313"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>295</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -23421,10 +23430,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="314"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -24194,19 +24203,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="322"/>
+      <c r="A1" s="319"/>
       <c r="B1" s="117"/>
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="323" t="s">
+      <c r="F1" s="348" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="323"/>
+      <c r="G1" s="348"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
-      <c r="K1" s="324"/>
+      <c r="K1" s="320"/>
     </row>
     <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="120" t="s">
@@ -24239,12 +24248,12 @@
       <c r="J2" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="325" t="s">
+      <c r="K2" s="321" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="326" t="s">
+      <c r="A3" s="322" t="s">
         <v>196</v>
       </c>
       <c r="B3" s="130" t="s">
@@ -24274,7 +24283,7 @@
       <c r="J3" s="267" t="s">
         <v>77</v>
       </c>
-      <c r="K3" s="327" t="s">
+      <c r="K3" s="323" t="s">
         <v>17</v>
       </c>
     </row>
@@ -24363,7 +24372,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="328" t="s">
+      <c r="A7" s="324" t="s">
         <v>114</v>
       </c>
       <c r="B7" s="224" t="s">
@@ -24392,7 +24401,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="326" t="s">
+      <c r="A8" s="322" t="s">
         <v>107</v>
       </c>
       <c r="B8" s="130" t="s">
@@ -24416,7 +24425,7 @@
       <c r="J8" s="133" t="s">
         <v>120</v>
       </c>
-      <c r="K8" s="327" t="s">
+      <c r="K8" s="323" t="s">
         <v>24</v>
       </c>
       <c r="L8" s="299"/>
@@ -24449,7 +24458,7 @@
       <c r="J9" s="133" t="s">
         <v>90</v>
       </c>
-      <c r="K9" s="329" t="s">
+      <c r="K9" s="325" t="s">
         <v>27</v>
       </c>
       <c r="L9" s="300"/>
@@ -24485,7 +24494,7 @@
       <c r="J10" s="133" t="s">
         <v>250</v>
       </c>
-      <c r="K10" s="327" t="s">
+      <c r="K10" s="323" t="s">
         <v>109</v>
       </c>
       <c r="L10" s="283"/>
@@ -24509,7 +24518,7 @@
       <c r="J11" s="133" t="s">
         <v>208</v>
       </c>
-      <c r="K11" s="327" t="s">
+      <c r="K11" s="323" t="s">
         <v>34</v>
       </c>
     </row>
@@ -24532,7 +24541,7 @@
       <c r="J12" s="143" t="s">
         <v>299</v>
       </c>
-      <c r="K12" s="327" t="s">
+      <c r="K12" s="323" t="s">
         <v>262</v>
       </c>
     </row>
@@ -24553,7 +24562,7 @@
       <c r="J13" s="143" t="s">
         <v>300</v>
       </c>
-      <c r="K13" s="330" t="s">
+      <c r="K13" s="326" t="s">
         <v>68</v>
       </c>
     </row>
@@ -24574,7 +24583,7 @@
       <c r="J14" s="143" t="s">
         <v>191</v>
       </c>
-      <c r="K14" s="331" t="s">
+      <c r="K14" s="327" t="s">
         <v>271</v>
       </c>
     </row>
@@ -24588,10 +24597,10 @@
       <c r="G15" s="150"/>
       <c r="H15" s="166"/>
       <c r="I15" s="140"/>
-      <c r="J15" s="318" t="s">
+      <c r="J15" s="315" t="s">
         <v>55</v>
       </c>
-      <c r="K15" s="332"/>
+      <c r="K15" s="328"/>
     </row>
     <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="120" t="s">
@@ -24621,7 +24630,7 @@
       <c r="I16" s="121" t="s">
         <v>100</v>
       </c>
-      <c r="K16" s="333"/>
+      <c r="K16" s="329"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="182" t="s">
@@ -24651,7 +24660,7 @@
       <c r="I17" s="68" t="s">
         <v>162</v>
       </c>
-      <c r="K17" s="334"/>
+      <c r="K17" s="330"/>
     </row>
     <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="120"/>
@@ -24666,7 +24675,7 @@
       <c r="H18" s="306"/>
       <c r="I18" s="157"/>
       <c r="J18" s="140"/>
-      <c r="K18" s="334"/>
+      <c r="K18" s="330"/>
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="185"/>
@@ -24704,18 +24713,18 @@
         <v>49</v>
       </c>
       <c r="H20" s="189"/>
-      <c r="I20" s="346" t="s">
+      <c r="I20" s="342" t="s">
         <v>50</v>
       </c>
-      <c r="J20" s="347" t="s">
+      <c r="J20" s="343" t="s">
         <v>51</v>
       </c>
-      <c r="K20" s="348" t="s">
+      <c r="K20" s="344" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A21" s="335" t="s">
+      <c r="A21" s="331" t="s">
         <v>153</v>
       </c>
       <c r="B21" s="133" t="s">
@@ -24730,20 +24739,20 @@
       <c r="F21" s="267" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="267" t="s">
-        <v>184</v>
+      <c r="G21" s="139" t="s">
+        <v>164</v>
       </c>
       <c r="H21" s="189"/>
-      <c r="I21" s="344" t="s">
+      <c r="I21" s="340" t="s">
         <v>112</v>
       </c>
       <c r="J21" s="198" t="s">
         <v>201</v>
       </c>
-      <c r="K21" s="345"/>
+      <c r="K21" s="341"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A22" s="335" t="s">
+      <c r="A22" s="331" t="s">
         <v>264</v>
       </c>
       <c r="B22" s="133" t="s">
@@ -24760,7 +24769,7 @@
         <v>97</v>
       </c>
       <c r="G22" s="133" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="H22" s="189"/>
       <c r="I22" s="197" t="s">
@@ -24772,7 +24781,7 @@
       <c r="K22" s="194"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A23" s="336" t="s">
+      <c r="A23" s="332" t="s">
         <v>126</v>
       </c>
       <c r="B23" s="133" t="s">
@@ -24784,12 +24793,12 @@
       </c>
       <c r="E23" s="165"/>
       <c r="F23" s="157"/>
-      <c r="G23" s="133" t="s">
-        <v>145</v>
+      <c r="G23" s="143" t="s">
+        <v>144</v>
       </c>
       <c r="H23" s="189"/>
       <c r="I23" s="197" t="s">
-        <v>63</v>
+        <v>268</v>
       </c>
       <c r="J23" s="207" t="s">
         <v>149</v>
@@ -24797,7 +24806,7 @@
       <c r="K23" s="203"/>
     </row>
     <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="335" t="s">
+      <c r="A24" s="331" t="s">
         <v>154</v>
       </c>
       <c r="B24" s="143" t="s">
@@ -24807,12 +24816,9 @@
       <c r="D24" s="205"/>
       <c r="E24" s="234"/>
       <c r="F24" s="234"/>
-      <c r="G24" s="133" t="s">
-        <v>136</v>
-      </c>
       <c r="H24" s="156"/>
       <c r="I24" s="197" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="J24" s="207" t="s">
         <v>159</v>
@@ -24820,7 +24826,7 @@
       <c r="K24" s="194"/>
     </row>
     <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="336" t="s">
+      <c r="A25" s="332" t="s">
         <v>122</v>
       </c>
       <c r="B25" s="234"/>
@@ -24839,7 +24845,7 @@
       <c r="K25" s="203"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A26" s="336" t="s">
+      <c r="A26" s="332" t="s">
         <v>123</v>
       </c>
       <c r="B26" s="234"/>
@@ -24852,15 +24858,15 @@
       <c r="G26" s="130"/>
       <c r="H26" s="204"/>
       <c r="I26" s="197" t="s">
-        <v>277</v>
-      </c>
-      <c r="J26" s="193" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="351" t="s">
         <v>73</v>
       </c>
       <c r="K26" s="203"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A27" s="335" t="s">
+      <c r="A27" s="331" t="s">
         <v>125</v>
       </c>
       <c r="B27" s="205"/>
@@ -24870,11 +24876,11 @@
       <c r="F27" s="133"/>
       <c r="G27" s="133"/>
       <c r="H27" s="287"/>
-      <c r="I27" s="197" t="s">
-        <v>52</v>
-      </c>
-      <c r="J27" s="207"/>
-      <c r="K27" s="203"/>
+      <c r="I27" s="349" t="s">
+        <v>63</v>
+      </c>
+      <c r="J27" s="237"/>
+      <c r="K27" s="350"/>
     </row>
     <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="195"/>
@@ -24888,7 +24894,7 @@
       <c r="I28" s="213" t="s">
         <v>54</v>
       </c>
-      <c r="J28" s="207"/>
+      <c r="J28" s="198"/>
       <c r="K28" s="210" t="s">
         <v>65</v>
       </c>
@@ -24908,12 +24914,12 @@
         <v>32</v>
       </c>
       <c r="J29" s="207"/>
-      <c r="K29" s="319" t="s">
+      <c r="K29" s="316" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="337"/>
+      <c r="A30" s="333"/>
       <c r="B30" s="157"/>
       <c r="C30" s="207"/>
       <c r="D30" s="157"/>
@@ -24928,17 +24934,17 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="338"/>
-      <c r="B31" s="339"/>
+      <c r="A31" s="334"/>
+      <c r="B31" s="335"/>
       <c r="C31" s="220"/>
-      <c r="D31" s="339"/>
-      <c r="E31" s="340"/>
-      <c r="F31" s="341"/>
-      <c r="G31" s="342"/>
-      <c r="H31" s="343"/>
-      <c r="I31" s="320"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="337"/>
+      <c r="G31" s="338"/>
+      <c r="H31" s="339"/>
+      <c r="I31" s="317"/>
       <c r="J31" s="220"/>
-      <c r="K31" s="321" t="s">
+      <c r="K31" s="318" t="s">
         <v>70</v>
       </c>
     </row>
@@ -24979,10 +24985,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="345" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="346"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25893,10 +25899,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="345" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="346"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -26809,10 +26815,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="315" t="s">
+      <c r="F1" s="345" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="316"/>
+      <c r="G1" s="346"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -27727,10 +27733,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -28645,10 +28651,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -29558,10 +29564,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="317" t="s">
+      <c r="F1" s="347" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="317"/>
+      <c r="G1" s="347"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7828976D-0AF0-4970-842C-432CF9BAB072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06E34D0-A7C7-4CAE-B5AE-CD423E3A9352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="13" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="15" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -40,6 +40,9 @@
     <sheet name="24" sheetId="175" r:id="rId30"/>
     <sheet name="25" sheetId="176" r:id="rId31"/>
     <sheet name="25.10 түскі ауысым" sheetId="177" r:id="rId32"/>
+    <sheet name="26.10" sheetId="178" r:id="rId33"/>
+    <sheet name="Лист2" sheetId="179" r:id="rId34"/>
+    <sheet name="Лист3" sheetId="180" r:id="rId35"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -140,7 +143,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5597" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5772" uniqueCount="306">
   <si>
     <t>СБ</t>
   </si>
@@ -1064,6 +1067,18 @@
   <si>
     <t>13-033ATQ01н</t>
   </si>
+  <si>
+    <t>C13-H1074/12</t>
+  </si>
+  <si>
+    <t>13-Н2663/12</t>
+  </si>
+  <si>
+    <t>51-Н2412/12н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.10.2026 ж </t>
+  </si>
 </sst>
 </file>
 
@@ -1072,7 +1087,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1252,6 +1267,14 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF660033"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1309,7 +1332,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1714,32 +1737,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -1789,7 +1786,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2727,16 +2724,22 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="3" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="3" borderId="33" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="3" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="3" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2751,13 +2754,16 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2775,11 +2781,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0F0FF9"/>
+      <color rgb="FF660033"/>
       <color rgb="FFFF99FF"/>
-      <color rgb="FF0F0FF9"/>
       <color rgb="FFFF66FF"/>
       <color rgb="FFFF00FF"/>
-      <color rgb="FF660033"/>
       <color rgb="FF00602B"/>
       <color rgb="FF007635"/>
     </mruColors>
@@ -3080,10 +3086,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="345" t="s">
+      <c r="F1" s="347" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="346"/>
+      <c r="G1" s="348"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -4132,10 +4138,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5041,10 +5047,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5961,10 +5967,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6875,10 +6881,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7801,10 +7807,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8725,10 +8731,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9644,10 +9650,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10565,10 +10571,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11485,10 +11491,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12270,10 +12276,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -13053,10 +13059,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="345" t="s">
+      <c r="F1" s="347" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="346"/>
+      <c r="G1" s="348"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13957,10 +13963,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14735,10 +14741,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15513,10 +15519,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16289,10 +16295,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17065,10 +17071,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17841,10 +17847,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18619,10 +18625,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19396,10 +19402,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="310"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20174,10 +20180,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="311"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20954,10 +20960,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="312"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>290</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21745,10 +21751,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="345" t="s">
+      <c r="F1" s="347" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="346"/>
+      <c r="G1" s="348"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22649,10 +22655,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="313"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>295</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -23430,10 +23436,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="314"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -24208,10 +24214,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="348" t="s">
+      <c r="F1" s="350" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="348"/>
+      <c r="G1" s="350"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -24630,6 +24636,7 @@
       <c r="I16" s="121" t="s">
         <v>100</v>
       </c>
+      <c r="J16" s="140"/>
       <c r="K16" s="329"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -24658,7 +24665,7 @@
         <v>11</v>
       </c>
       <c r="I17" s="68" t="s">
-        <v>162</v>
+        <v>302</v>
       </c>
       <c r="K17" s="330"/>
     </row>
@@ -24713,13 +24720,13 @@
         <v>49</v>
       </c>
       <c r="H20" s="189"/>
-      <c r="I20" s="342" t="s">
+      <c r="I20" s="340" t="s">
         <v>50</v>
       </c>
-      <c r="J20" s="343" t="s">
+      <c r="J20" s="341" t="s">
         <v>51</v>
       </c>
-      <c r="K20" s="344" t="s">
+      <c r="K20" s="342" t="s">
         <v>51</v>
       </c>
     </row>
@@ -24743,13 +24750,13 @@
         <v>164</v>
       </c>
       <c r="H21" s="189"/>
-      <c r="I21" s="340" t="s">
+      <c r="I21" s="351" t="s">
         <v>112</v>
       </c>
-      <c r="J21" s="198" t="s">
+      <c r="J21" s="352" t="s">
         <v>201</v>
       </c>
-      <c r="K21" s="341"/>
+      <c r="K21" s="225"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="331" t="s">
@@ -24794,11 +24801,11 @@
       <c r="E23" s="165"/>
       <c r="F23" s="157"/>
       <c r="G23" s="143" t="s">
-        <v>144</v>
+        <v>304</v>
       </c>
       <c r="H23" s="189"/>
       <c r="I23" s="197" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="J23" s="207" t="s">
         <v>149</v>
@@ -24818,7 +24825,7 @@
       <c r="F24" s="234"/>
       <c r="H24" s="156"/>
       <c r="I24" s="197" t="s">
-        <v>277</v>
+        <v>186</v>
       </c>
       <c r="J24" s="207" t="s">
         <v>159</v>
@@ -24837,7 +24844,7 @@
       <c r="G25" s="139"/>
       <c r="H25" s="189"/>
       <c r="I25" s="197" t="s">
-        <v>186</v>
+        <v>303</v>
       </c>
       <c r="J25" s="207" t="s">
         <v>84</v>
@@ -24860,7 +24867,7 @@
       <c r="I26" s="197" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="351" t="s">
+      <c r="J26" s="346" t="s">
         <v>73</v>
       </c>
       <c r="K26" s="203"/>
@@ -24874,13 +24881,13 @@
       <c r="D27" s="205"/>
       <c r="E27" s="133"/>
       <c r="F27" s="133"/>
-      <c r="G27" s="133"/>
+      <c r="G27" s="68"/>
       <c r="H27" s="287"/>
-      <c r="I27" s="349" t="s">
+      <c r="I27" s="344" t="s">
         <v>63</v>
       </c>
       <c r="J27" s="237"/>
-      <c r="K27" s="350"/>
+      <c r="K27" s="345"/>
     </row>
     <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="195"/>
@@ -24927,7 +24934,9 @@
       <c r="F30" s="157"/>
       <c r="G30" s="244"/>
       <c r="H30" s="189"/>
-      <c r="I30" s="197"/>
+      <c r="I30" s="353" t="s">
+        <v>181</v>
+      </c>
       <c r="J30" s="207"/>
       <c r="K30" s="179" t="s">
         <v>103</v>
@@ -24956,6 +24965,795 @@
   <mergeCells count="1">
     <mergeCell ref="F1:G1"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18DE9DD8-908A-4494-8ACF-E67E76036F94}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="11" width="11.81640625" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.90625" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="319"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="343"/>
+      <c r="F1" s="350" t="s">
+        <v>305</v>
+      </c>
+      <c r="G1" s="350"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="320"/>
+    </row>
+    <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="322" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="323" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="137" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="145"/>
+      <c r="B5" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="136" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="137"/>
+      <c r="B6" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="156" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="159" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="138"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="136" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="324" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="136" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="322" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="K8" s="323" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="133" t="s">
+        <v>135</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>90</v>
+      </c>
+      <c r="K9" s="325" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="137" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="235" t="s">
+        <v>259</v>
+      </c>
+      <c r="I10" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="133" t="s">
+        <v>250</v>
+      </c>
+      <c r="K10" s="323" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="137"/>
+      <c r="B11" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="133" t="s">
+        <v>208</v>
+      </c>
+      <c r="K11" s="323" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="169" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="267" t="s">
+        <v>291</v>
+      </c>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="143" t="s">
+        <v>299</v>
+      </c>
+      <c r="K12" s="323" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="137" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="256" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="234"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="143" t="s">
+        <v>300</v>
+      </c>
+      <c r="K13" s="326" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="137" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="262" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="143" t="s">
+        <v>191</v>
+      </c>
+      <c r="K14" s="327" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="177"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="315" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="328"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="120" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="140"/>
+      <c r="K16" s="329"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="182" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="K17" s="330"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="120"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="330"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="185"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="188"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="120" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="189"/>
+      <c r="I20" s="340" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="341" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="342" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="331" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="187" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="141" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="189"/>
+      <c r="I21" s="351" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="352" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="225"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="331" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="141"/>
+      <c r="D22" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="189"/>
+      <c r="I22" s="197" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="354" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" s="194"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="332" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="133" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="133"/>
+      <c r="D23" s="267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="143" t="s">
+        <v>304</v>
+      </c>
+      <c r="H23" s="189"/>
+      <c r="I23" s="197" t="s">
+        <v>186</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K23" s="203"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="331" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="143" t="s">
+        <v>298</v>
+      </c>
+      <c r="C24" s="234"/>
+      <c r="D24" s="205"/>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="H24" s="156"/>
+      <c r="I24" s="197" t="s">
+        <v>303</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K24" s="194"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="332" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="157"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="189"/>
+      <c r="I25" s="197" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K25" s="203"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="332" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="205"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="204"/>
+      <c r="I26" s="344" t="s">
+        <v>63</v>
+      </c>
+      <c r="J26" s="207" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="203"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" s="331" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="287"/>
+      <c r="I27" s="213" t="s">
+        <v>54</v>
+      </c>
+      <c r="J27" s="237"/>
+      <c r="K27" s="345"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="195"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="287"/>
+      <c r="I28" s="213" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" s="198"/>
+      <c r="K28" s="210" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="195"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="353" t="s">
+        <v>181</v>
+      </c>
+      <c r="J29" s="207"/>
+      <c r="K29" s="316" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="333"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="189"/>
+      <c r="I30" s="353"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="179" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="334"/>
+      <c r="B31" s="335"/>
+      <c r="C31" s="220"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="337"/>
+      <c r="G31" s="338"/>
+      <c r="H31" s="339"/>
+      <c r="I31" s="317"/>
+      <c r="J31" s="220"/>
+      <c r="K31" s="318" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938EEC82-C52B-4B37-8642-02394F8FD5A9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC28A956-A9D4-4F2E-868C-CF026C498D3A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -24985,10 +25783,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="345" t="s">
+      <c r="F1" s="347" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="346"/>
+      <c r="G1" s="348"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25899,10 +26697,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="345" t="s">
+      <c r="F1" s="347" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="346"/>
+      <c r="G1" s="348"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -26815,10 +27613,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="345" t="s">
+      <c r="F1" s="347" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="346"/>
+      <c r="G1" s="348"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -27733,10 +28531,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -28651,10 +29449,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -29564,10 +30362,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="349" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="347"/>
+      <c r="G1" s="349"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06E34D0-A7C7-4CAE-B5AE-CD423E3A9352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9888067-2E73-48F9-88DF-FB4DFBD440E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="15" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="17" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <sheet name="25" sheetId="176" r:id="rId31"/>
     <sheet name="25.10 түскі ауысым" sheetId="177" r:id="rId32"/>
     <sheet name="26.10" sheetId="178" r:id="rId33"/>
-    <sheet name="Лист2" sheetId="179" r:id="rId34"/>
+    <sheet name="27.10" sheetId="179" r:id="rId34"/>
     <sheet name="Лист3" sheetId="180" r:id="rId35"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -142,8 +142,43 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{35D03E37-2FA0-4AFC-B580-2C52568BFFE5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Түс қайта</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5772" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5947" uniqueCount="310">
   <si>
     <t>СБ</t>
   </si>
@@ -1071,13 +1106,25 @@
     <t>C13-H1074/12</t>
   </si>
   <si>
-    <t>13-Н2663/12</t>
-  </si>
-  <si>
     <t>51-Н2412/12н</t>
   </si>
   <si>
     <t xml:space="preserve">26.10.2026 ж </t>
+  </si>
+  <si>
+    <t>С13-Н2663/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.10.2026 ж </t>
+  </si>
+  <si>
+    <t>С13-H2718/12н</t>
+  </si>
+  <si>
+    <t>34-Н2795/12</t>
+  </si>
+  <si>
+    <t>13-Н1293/12</t>
   </si>
 </sst>
 </file>
@@ -1786,7 +1833,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2742,15 +2789,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2764,6 +2802,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2781,8 +2833,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF660033"/>
       <color rgb="FF0F0FF9"/>
-      <color rgb="FF660033"/>
       <color rgb="FFFF99FF"/>
       <color rgb="FFFF66FF"/>
       <color rgb="FFFF00FF"/>
@@ -3086,10 +3138,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="354" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="348"/>
+      <c r="G1" s="355"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -4138,10 +4190,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5047,10 +5099,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5967,10 +6019,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6881,10 +6933,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7807,10 +7859,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8731,10 +8783,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9650,10 +9702,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10571,10 +10623,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11491,10 +11543,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12276,10 +12328,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -13059,10 +13111,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="354" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="348"/>
+      <c r="G1" s="355"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -13963,10 +14015,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14741,10 +14793,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15519,10 +15571,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16295,10 +16347,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17071,10 +17123,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17847,10 +17899,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18625,10 +18677,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19402,10 +19454,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="310"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20180,10 +20232,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="311"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20960,10 +21012,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="312"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>290</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21751,10 +21803,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="354" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="348"/>
+      <c r="G1" s="355"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22655,10 +22707,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="313"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>295</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -23436,10 +23488,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="314"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -24214,10 +24266,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="350" t="s">
+      <c r="F1" s="357" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="350"/>
+      <c r="G1" s="357"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -24678,8 +24730,10 @@
       <c r="F18" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="157"/>
-      <c r="H18" s="306"/>
+      <c r="G18" s="353"/>
+      <c r="H18" s="159" t="s">
+        <v>305</v>
+      </c>
       <c r="I18" s="157"/>
       <c r="J18" s="140"/>
       <c r="K18" s="330"/>
@@ -24750,10 +24804,10 @@
         <v>164</v>
       </c>
       <c r="H21" s="189"/>
-      <c r="I21" s="351" t="s">
+      <c r="I21" s="348" t="s">
         <v>112</v>
       </c>
-      <c r="J21" s="352" t="s">
+      <c r="J21" s="349" t="s">
         <v>201</v>
       </c>
       <c r="K21" s="225"/>
@@ -24801,7 +24855,7 @@
       <c r="E23" s="165"/>
       <c r="F23" s="157"/>
       <c r="G23" s="143" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H23" s="189"/>
       <c r="I23" s="197" t="s">
@@ -24844,7 +24898,7 @@
       <c r="G25" s="139"/>
       <c r="H25" s="189"/>
       <c r="I25" s="197" t="s">
-        <v>303</v>
+        <v>52</v>
       </c>
       <c r="J25" s="207" t="s">
         <v>84</v>
@@ -24864,8 +24918,8 @@
       <c r="F26" s="139"/>
       <c r="G26" s="130"/>
       <c r="H26" s="204"/>
-      <c r="I26" s="197" t="s">
-        <v>52</v>
+      <c r="I26" s="344" t="s">
+        <v>63</v>
       </c>
       <c r="J26" s="346" t="s">
         <v>73</v>
@@ -24883,8 +24937,8 @@
       <c r="F27" s="133"/>
       <c r="G27" s="68"/>
       <c r="H27" s="287"/>
-      <c r="I27" s="344" t="s">
-        <v>63</v>
+      <c r="I27" s="213" t="s">
+        <v>54</v>
       </c>
       <c r="J27" s="237"/>
       <c r="K27" s="345"/>
@@ -24899,7 +24953,7 @@
       <c r="G28" s="16"/>
       <c r="H28" s="287"/>
       <c r="I28" s="213" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="J28" s="198"/>
       <c r="K28" s="210" t="s">
@@ -24917,8 +24971,8 @@
       </c>
       <c r="G29" s="157"/>
       <c r="H29" s="189"/>
-      <c r="I29" s="213" t="s">
-        <v>32</v>
+      <c r="I29" s="350" t="s">
+        <v>181</v>
       </c>
       <c r="J29" s="207"/>
       <c r="K29" s="316" t="s">
@@ -24934,9 +24988,7 @@
       <c r="F30" s="157"/>
       <c r="G30" s="244"/>
       <c r="H30" s="189"/>
-      <c r="I30" s="353" t="s">
-        <v>181</v>
-      </c>
+      <c r="I30" s="352"/>
       <c r="J30" s="207"/>
       <c r="K30" s="179" t="s">
         <v>103</v>
@@ -24984,10 +25036,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="343"/>
-      <c r="F1" s="350" t="s">
-        <v>305</v>
-      </c>
-      <c r="G1" s="350"/>
+      <c r="F1" s="357" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1" s="357"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25451,7 +25503,9 @@
         <v>47</v>
       </c>
       <c r="G18" s="157"/>
-      <c r="H18" s="306"/>
+      <c r="H18" s="159" t="s">
+        <v>305</v>
+      </c>
       <c r="I18" s="157"/>
       <c r="J18" s="140"/>
       <c r="K18" s="330"/>
@@ -25525,10 +25579,10 @@
         <v>164</v>
       </c>
       <c r="H21" s="189"/>
-      <c r="I21" s="351" t="s">
+      <c r="I21" s="348" t="s">
         <v>112</v>
       </c>
-      <c r="J21" s="352" t="s">
+      <c r="J21" s="349" t="s">
         <v>201</v>
       </c>
       <c r="K21" s="225"/>
@@ -25555,7 +25609,7 @@
       <c r="I22" s="197" t="s">
         <v>163</v>
       </c>
-      <c r="J22" s="354" t="s">
+      <c r="J22" s="351" t="s">
         <v>33</v>
       </c>
       <c r="K22" s="194"/>
@@ -25574,7 +25628,7 @@
       <c r="E23" s="165"/>
       <c r="F23" s="157"/>
       <c r="G23" s="143" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H23" s="189"/>
       <c r="I23" s="197" t="s">
@@ -25598,7 +25652,7 @@
       <c r="F24" s="234"/>
       <c r="H24" s="156"/>
       <c r="I24" s="197" t="s">
-        <v>303</v>
+        <v>52</v>
       </c>
       <c r="J24" s="207" t="s">
         <v>149</v>
@@ -25616,8 +25670,8 @@
       <c r="F25" s="157"/>
       <c r="G25" s="139"/>
       <c r="H25" s="189"/>
-      <c r="I25" s="197" t="s">
-        <v>52</v>
+      <c r="I25" s="344" t="s">
+        <v>63</v>
       </c>
       <c r="J25" s="207" t="s">
         <v>159</v>
@@ -25637,8 +25691,8 @@
       <c r="F26" s="139"/>
       <c r="G26" s="130"/>
       <c r="H26" s="204"/>
-      <c r="I26" s="344" t="s">
-        <v>63</v>
+      <c r="I26" s="213" t="s">
+        <v>54</v>
       </c>
       <c r="J26" s="207" t="s">
         <v>84</v>
@@ -25657,7 +25711,7 @@
       <c r="G27" s="68"/>
       <c r="H27" s="287"/>
       <c r="I27" s="213" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="J27" s="237"/>
       <c r="K27" s="345"/>
@@ -25671,8 +25725,8 @@
       <c r="F28" s="166"/>
       <c r="G28" s="16"/>
       <c r="H28" s="287"/>
-      <c r="I28" s="213" t="s">
-        <v>32</v>
+      <c r="I28" s="350" t="s">
+        <v>181</v>
       </c>
       <c r="J28" s="198"/>
       <c r="K28" s="210" t="s">
@@ -25690,9 +25744,7 @@
       </c>
       <c r="G29" s="157"/>
       <c r="H29" s="189"/>
-      <c r="I29" s="353" t="s">
-        <v>181</v>
-      </c>
+      <c r="I29" s="350"/>
       <c r="J29" s="207"/>
       <c r="K29" s="316" t="s">
         <v>88</v>
@@ -25707,7 +25759,7 @@
       <c r="F30" s="157"/>
       <c r="G30" s="244"/>
       <c r="H30" s="189"/>
-      <c r="I30" s="353"/>
+      <c r="I30" s="350"/>
       <c r="J30" s="207"/>
       <c r="K30" s="179" t="s">
         <v>103</v>
@@ -25741,11 +25793,776 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938EEC82-C52B-4B37-8642-02394F8FD5A9}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938EEC82-C52B-4B37-8642-02394F8FD5A9}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="11" width="11.81640625" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.90625" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="319"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="347"/>
+      <c r="F1" s="357" t="s">
+        <v>306</v>
+      </c>
+      <c r="G1" s="357"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="320"/>
+    </row>
+    <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="322" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="323" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="137" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="145"/>
+      <c r="B5" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="156" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="136" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="137"/>
+      <c r="B6" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="136" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="324" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="130"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="136" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="322" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="K8" s="323" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="130" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="164" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="140" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>90</v>
+      </c>
+      <c r="K9" s="325" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="137" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="235" t="s">
+        <v>259</v>
+      </c>
+      <c r="I10" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="133" t="s">
+        <v>250</v>
+      </c>
+      <c r="K10" s="323" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="137"/>
+      <c r="B11" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="133" t="s">
+        <v>208</v>
+      </c>
+      <c r="K11" s="323" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="169" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="143" t="s">
+        <v>299</v>
+      </c>
+      <c r="K12" s="323" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="137" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="143" t="s">
+        <v>300</v>
+      </c>
+      <c r="K13" s="326" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="137" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="263" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="143" t="s">
+        <v>191</v>
+      </c>
+      <c r="K14" s="327" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="177"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="141" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="328"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="120" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="329"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="182" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="K17" s="330"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="120"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="159"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="330"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="185"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="188"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="120" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="189"/>
+      <c r="I20" s="340" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="341" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="342" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="331" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="187" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="133" t="s">
+        <v>308</v>
+      </c>
+      <c r="E21" s="141" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="189"/>
+      <c r="I21" s="348" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="349" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="225"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="331" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="141"/>
+      <c r="D22" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="189"/>
+      <c r="I22" s="197" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="194"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="332" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="133" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="143" t="s">
+        <v>303</v>
+      </c>
+      <c r="H23" s="189"/>
+      <c r="I23" s="197" t="s">
+        <v>309</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="203"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="331" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="143" t="s">
+        <v>298</v>
+      </c>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="H24" s="156"/>
+      <c r="I24" s="197" t="s">
+        <v>186</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="194"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="332" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="157"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="189"/>
+      <c r="I25" s="197" t="s">
+        <v>305</v>
+      </c>
+      <c r="J25" s="351" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" s="203"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="332" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="205"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="204"/>
+      <c r="I26" s="213" t="s">
+        <v>241</v>
+      </c>
+      <c r="J26" s="237"/>
+      <c r="K26" s="203"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" s="331" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="287"/>
+      <c r="I27" s="197" t="s">
+        <v>52</v>
+      </c>
+      <c r="J27" s="237"/>
+      <c r="K27" s="203"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="195"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="287"/>
+      <c r="I28" s="197" t="s">
+        <v>63</v>
+      </c>
+      <c r="J28" s="207"/>
+      <c r="K28" s="210" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="195"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="350" t="s">
+        <v>84</v>
+      </c>
+      <c r="J29" s="207"/>
+      <c r="K29" s="316" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="333"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="189"/>
+      <c r="I30" s="350" t="s">
+        <v>181</v>
+      </c>
+      <c r="J30" s="207"/>
+      <c r="K30" s="179" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="334"/>
+      <c r="B31" s="335"/>
+      <c r="C31" s="220"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="337"/>
+      <c r="G31" s="338"/>
+      <c r="H31" s="339"/>
+      <c r="I31" s="317"/>
+      <c r="J31" s="220"/>
+      <c r="K31" s="318" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -25783,10 +26600,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="354" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="348"/>
+      <c r="G1" s="355"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -26697,10 +27514,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="354" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="348"/>
+      <c r="G1" s="355"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -27613,10 +28430,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="347" t="s">
+      <c r="F1" s="354" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="348"/>
+      <c r="G1" s="355"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -28531,10 +29348,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -29449,10 +30266,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -30362,10 +31179,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="349" t="s">
+      <c r="F1" s="356" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="349"/>
+      <c r="G1" s="356"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9888067-2E73-48F9-88DF-FB4DFBD440E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8DFF9CC-E471-47AC-86CF-A61904E01ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="17" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="21" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -42,7 +42,8 @@
     <sheet name="25.10 түскі ауысым" sheetId="177" r:id="rId32"/>
     <sheet name="26.10" sheetId="178" r:id="rId33"/>
     <sheet name="27.10" sheetId="179" r:id="rId34"/>
-    <sheet name="Лист3" sheetId="180" r:id="rId35"/>
+    <sheet name="27.10 Түскі ауысым" sheetId="180" r:id="rId35"/>
+    <sheet name="28.10" sheetId="181" r:id="rId36"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -177,8 +178,44 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{8EF85B60-91FB-4237-B006-CB729373CF39}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Түс қайта шығады</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5947" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6294" uniqueCount="311">
   <si>
     <t>СБ</t>
   </si>
@@ -1126,6 +1163,9 @@
   <si>
     <t>13-Н1293/12</t>
   </si>
+  <si>
+    <t xml:space="preserve">28.10.2026 ж </t>
+  </si>
 </sst>
 </file>
 
@@ -1134,7 +1174,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1319,6 +1359,13 @@
       <sz val="8"/>
       <color rgb="FF660033"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -1833,7 +1880,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="365">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2804,8 +2851,31 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2833,8 +2903,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0F0FF9"/>
       <color rgb="FF660033"/>
-      <color rgb="FF0F0FF9"/>
       <color rgb="FFFF99FF"/>
       <color rgb="FFFF66FF"/>
       <color rgb="FFFF00FF"/>
@@ -3138,10 +3208,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="354" t="s">
+      <c r="F1" s="361" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="355"/>
+      <c r="G1" s="362"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -4190,10 +4260,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5099,10 +5169,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6019,10 +6089,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6933,10 +7003,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7859,10 +7929,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8783,10 +8853,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9702,10 +9772,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10623,10 +10693,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11543,10 +11613,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12328,10 +12398,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -13111,10 +13181,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="354" t="s">
+      <c r="F1" s="361" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="355"/>
+      <c r="G1" s="362"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -14015,10 +14085,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14793,10 +14863,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15571,10 +15641,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16347,10 +16417,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17123,10 +17193,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17899,10 +17969,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18677,10 +18747,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19454,10 +19524,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="310"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20232,10 +20302,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="311"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21012,10 +21082,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="312"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>290</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21803,10 +21873,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="354" t="s">
+      <c r="F1" s="361" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="355"/>
+      <c r="G1" s="362"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22707,10 +22777,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="313"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>295</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -23488,10 +23558,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="314"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -24266,10 +24336,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="357" t="s">
+      <c r="F1" s="364" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="357"/>
+      <c r="G1" s="364"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -24568,7 +24638,7 @@
       </c>
       <c r="E11" s="166"/>
       <c r="F11" s="166"/>
-      <c r="G11" s="267" t="s">
+      <c r="G11" s="143" t="s">
         <v>291</v>
       </c>
       <c r="H11" s="140"/>
@@ -24730,7 +24800,7 @@
       <c r="F18" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="353"/>
+      <c r="G18" s="352"/>
       <c r="H18" s="159" t="s">
         <v>305</v>
       </c>
@@ -24788,13 +24858,10 @@
       <c r="A21" s="331" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="133" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="133" t="s">
+      <c r="D21" s="139" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="141" t="s">
+      <c r="E21" s="354" t="s">
         <v>64</v>
       </c>
       <c r="F21" s="267" t="s">
@@ -24816,20 +24883,18 @@
       <c r="A22" s="331" t="s">
         <v>264</v>
       </c>
-      <c r="B22" s="133" t="s">
+      <c r="B22" s="139" t="s">
         <v>111</v>
       </c>
-      <c r="C22" s="141" t="s">
-        <v>280</v>
-      </c>
-      <c r="D22" s="133" t="s">
+      <c r="C22" s="141"/>
+      <c r="D22" s="139" t="s">
         <v>182</v>
       </c>
       <c r="E22" s="160"/>
       <c r="F22" s="130" t="s">
         <v>97</v>
       </c>
-      <c r="G22" s="133" t="s">
+      <c r="G22" s="139" t="s">
         <v>145</v>
       </c>
       <c r="H22" s="189"/>
@@ -24845,11 +24910,11 @@
       <c r="A23" s="332" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="133" t="s">
+      <c r="B23" s="139" t="s">
         <v>174</v>
       </c>
       <c r="C23" s="133"/>
-      <c r="D23" s="267" t="s">
+      <c r="D23" s="143" t="s">
         <v>178</v>
       </c>
       <c r="E23" s="165"/>
@@ -24940,7 +25005,9 @@
       <c r="I27" s="213" t="s">
         <v>54</v>
       </c>
-      <c r="J27" s="237"/>
+      <c r="J27" s="355" t="s">
+        <v>83</v>
+      </c>
       <c r="K27" s="345"/>
     </row>
     <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -24988,7 +25055,9 @@
       <c r="F30" s="157"/>
       <c r="G30" s="244"/>
       <c r="H30" s="189"/>
-      <c r="I30" s="352"/>
+      <c r="I30" s="197" t="s">
+        <v>280</v>
+      </c>
       <c r="J30" s="207"/>
       <c r="K30" s="179" t="s">
         <v>103</v>
@@ -25036,10 +25105,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="343"/>
-      <c r="F1" s="357" t="s">
+      <c r="F1" s="364" t="s">
         <v>304</v>
       </c>
-      <c r="G1" s="357"/>
+      <c r="G1" s="364"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25563,9 +25632,6 @@
       <c r="B21" s="133" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="187" t="s">
-        <v>73</v>
-      </c>
       <c r="D21" s="133" t="s">
         <v>91</v>
       </c>
@@ -25713,7 +25779,9 @@
       <c r="I27" s="213" t="s">
         <v>32</v>
       </c>
-      <c r="J27" s="237"/>
+      <c r="J27" s="356" t="s">
+        <v>73</v>
+      </c>
       <c r="K27" s="345"/>
     </row>
     <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -25728,7 +25796,7 @@
       <c r="I28" s="350" t="s">
         <v>181</v>
       </c>
-      <c r="J28" s="198"/>
+      <c r="J28" s="207"/>
       <c r="K28" s="210" t="s">
         <v>65</v>
       </c>
@@ -25807,10 +25875,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="347"/>
-      <c r="F1" s="357" t="s">
+      <c r="F1" s="364" t="s">
         <v>306</v>
       </c>
-      <c r="G1" s="357"/>
+      <c r="G1" s="364"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -26090,9 +26158,7 @@
       <c r="H10" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="I10" s="133" t="s">
-        <v>56</v>
-      </c>
+      <c r="I10" s="133"/>
       <c r="J10" s="133" t="s">
         <v>250</v>
       </c>
@@ -26568,10 +26634,1543 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC28A956-A9D4-4F2E-868C-CF026C498D3A}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="11" width="11.81640625" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.90625" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="319"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="353"/>
+      <c r="F1" s="364" t="s">
+        <v>306</v>
+      </c>
+      <c r="G1" s="364"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="320"/>
+    </row>
+    <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="137" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="323" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="137" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="140" t="s">
+        <v>241</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="145"/>
+      <c r="B5" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="156" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="136" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="137"/>
+      <c r="B6" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="136" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="324" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="130"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="K7" s="136" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="137" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="323" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="130" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="164" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="140" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>250</v>
+      </c>
+      <c r="K9" s="325" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="129" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="235" t="s">
+        <v>259</v>
+      </c>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>208</v>
+      </c>
+      <c r="K10" s="323" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="137"/>
+      <c r="B11" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="143" t="s">
+        <v>299</v>
+      </c>
+      <c r="K11" s="323" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="169" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="143" t="s">
+        <v>300</v>
+      </c>
+      <c r="K12" s="323" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="137" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="143" t="s">
+        <v>191</v>
+      </c>
+      <c r="K13" s="326" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="137" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="263" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="293" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="327" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="177"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="359" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="120" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="140"/>
+      <c r="K16" s="329"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="182" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="K17" s="330"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="120"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="157"/>
+      <c r="H18" s="159"/>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="330"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="185"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="188"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="120" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="189"/>
+      <c r="I20" s="340" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="341" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="342" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="331" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="357" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="141" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="189"/>
+      <c r="I21" s="348" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="349" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="225"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="192" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="143" t="s">
+        <v>291</v>
+      </c>
+      <c r="D22" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="189"/>
+      <c r="I22" s="197" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="194"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="331" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" s="133" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="133"/>
+      <c r="D23" s="267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="143" t="s">
+        <v>303</v>
+      </c>
+      <c r="H23" s="189"/>
+      <c r="I23" s="213" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="203"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="192" t="s">
+        <v>198</v>
+      </c>
+      <c r="B24" s="143" t="s">
+        <v>298</v>
+      </c>
+      <c r="C24" s="234"/>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="H24" s="156"/>
+      <c r="I24" s="197" t="s">
+        <v>309</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="194"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="358" t="s">
+        <v>200</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="157"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="189"/>
+      <c r="I25" s="197" t="s">
+        <v>186</v>
+      </c>
+      <c r="J25" s="193" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" s="203"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="358" t="s">
+        <v>199</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="205"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="204"/>
+      <c r="I26" s="197" t="s">
+        <v>305</v>
+      </c>
+      <c r="J26" s="237"/>
+      <c r="K26" s="203"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" s="201" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="287"/>
+      <c r="I27" s="197" t="s">
+        <v>52</v>
+      </c>
+      <c r="J27" s="237"/>
+      <c r="K27" s="203"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="195"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="287"/>
+      <c r="I28" s="350" t="s">
+        <v>84</v>
+      </c>
+      <c r="J28" s="207"/>
+      <c r="K28" s="210" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="195"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="350" t="s">
+        <v>181</v>
+      </c>
+      <c r="J29" s="207"/>
+      <c r="K29" s="316" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="333"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="189"/>
+      <c r="I30" s="350"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="179" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="334"/>
+      <c r="B31" s="335"/>
+      <c r="C31" s="220"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="337"/>
+      <c r="G31" s="338"/>
+      <c r="H31" s="339"/>
+      <c r="I31" s="317"/>
+      <c r="J31" s="220"/>
+      <c r="K31" s="318" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004FCD42-6D78-4C91-B95F-2D1F5DBAA062}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="11" width="11.81640625" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.90625" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="319"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="353"/>
+      <c r="F1" s="364" t="s">
+        <v>310</v>
+      </c>
+      <c r="G1" s="364"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="320"/>
+    </row>
+    <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="137" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="323" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="137" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="140" t="s">
+        <v>241</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="133" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="145"/>
+      <c r="B5" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="156" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="136" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="137"/>
+      <c r="B6" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="136" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="324" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="130"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="K7" s="136" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="137" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="323" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="130" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="164" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>250</v>
+      </c>
+      <c r="K9" s="325" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="137" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="235" t="s">
+        <v>259</v>
+      </c>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>208</v>
+      </c>
+      <c r="K10" s="323" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="137"/>
+      <c r="B11" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="143" t="s">
+        <v>299</v>
+      </c>
+      <c r="K11" s="323" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="169" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="143" t="s">
+        <v>300</v>
+      </c>
+      <c r="K12" s="323" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="137" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="143" t="s">
+        <v>191</v>
+      </c>
+      <c r="K13" s="326" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="137" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="263" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="141" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="327" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="177"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="359" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="120" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="234"/>
+      <c r="K16" s="329"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="182" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="K17" s="330"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="120"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="352"/>
+      <c r="H18" s="159" t="s">
+        <v>305</v>
+      </c>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="330"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="185"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="188"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="120" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="189"/>
+      <c r="I20" s="340" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="341" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="342" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="331" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="166" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="141" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="189"/>
+      <c r="I21" s="348" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="349" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="225"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="192" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="360" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="189"/>
+      <c r="I22" s="197" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="194"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="331" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" s="133" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="143" t="s">
+        <v>291</v>
+      </c>
+      <c r="D23" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="143" t="s">
+        <v>303</v>
+      </c>
+      <c r="H23" s="189"/>
+      <c r="I23" s="213" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="203"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="192" t="s">
+        <v>198</v>
+      </c>
+      <c r="B24" s="143" t="s">
+        <v>298</v>
+      </c>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="H24" s="156"/>
+      <c r="I24" s="197" t="s">
+        <v>309</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="194"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="358" t="s">
+        <v>200</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="157"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="189"/>
+      <c r="I25" s="197" t="s">
+        <v>186</v>
+      </c>
+      <c r="J25" s="193" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" s="203"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="358" t="s">
+        <v>199</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="205"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="204"/>
+      <c r="I26" s="197" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="237"/>
+      <c r="K26" s="203"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" s="201" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="287"/>
+      <c r="I27" s="350" t="s">
+        <v>181</v>
+      </c>
+      <c r="J27" s="237"/>
+      <c r="K27" s="203"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="195"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="287"/>
+      <c r="I28" s="350"/>
+      <c r="J28" s="207"/>
+      <c r="K28" s="210" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="195"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="350"/>
+      <c r="J29" s="207"/>
+      <c r="K29" s="316" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="333"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="189"/>
+      <c r="I30" s="350"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="179" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="334"/>
+      <c r="B31" s="335"/>
+      <c r="C31" s="220"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="337"/>
+      <c r="G31" s="338"/>
+      <c r="H31" s="339"/>
+      <c r="I31" s="317"/>
+      <c r="J31" s="220"/>
+      <c r="K31" s="318" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -26600,10 +28199,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="354" t="s">
+      <c r="F1" s="361" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="355"/>
+      <c r="G1" s="362"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -27514,10 +29113,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="354" t="s">
+      <c r="F1" s="361" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="355"/>
+      <c r="G1" s="362"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -28430,10 +30029,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="354" t="s">
+      <c r="F1" s="361" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="355"/>
+      <c r="G1" s="362"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -29348,10 +30947,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -30266,10 +31865,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -31179,10 +32778,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="356" t="s">
+      <c r="F1" s="363" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="356"/>
+      <c r="G1" s="363"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8DFF9CC-E471-47AC-86CF-A61904E01ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D176BE15-88C5-4E9C-A22B-97E5C8DAA045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="21" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="23" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -44,6 +44,7 @@
     <sheet name="27.10" sheetId="179" r:id="rId34"/>
     <sheet name="27.10 Түскі ауысым" sheetId="180" r:id="rId35"/>
     <sheet name="28.10" sheetId="181" r:id="rId36"/>
+    <sheet name="29.10" sheetId="182" r:id="rId37"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -122,7 +123,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -131,7 +133,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 8 702 489 68 89
@@ -167,7 +170,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Түс қайта</t>
@@ -215,7 +219,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6294" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6467" uniqueCount="316">
   <si>
     <t>СБ</t>
   </si>
@@ -1166,6 +1170,21 @@
   <si>
     <t xml:space="preserve">28.10.2026 ж </t>
   </si>
+  <si>
+    <t>С12-H1109/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.10.2026 ж </t>
+  </si>
+  <si>
+    <t>С13-H290АН/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-Н798399 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">С12-Н798399 </t>
+  </si>
 </sst>
 </file>
 
@@ -1174,7 +1193,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1345,27 +1364,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color rgb="FF660033"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -1880,7 +1886,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="365">
+  <cellXfs count="366">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2848,7 +2854,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2858,10 +2864,10 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2873,7 +2879,7 @@
     <xf numFmtId="9" fontId="3" fillId="3" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2886,6 +2892,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2903,8 +2912,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF660033"/>
       <color rgb="FF0F0FF9"/>
-      <color rgb="FF660033"/>
       <color rgb="FFFF99FF"/>
       <color rgb="FFFF66FF"/>
       <color rgb="FFFF00FF"/>
@@ -26750,8 +26759,8 @@
         <v>118</v>
       </c>
       <c r="I4" s="150"/>
-      <c r="J4" s="133" t="s">
-        <v>13</v>
+      <c r="J4" s="130" t="s">
+        <v>311</v>
       </c>
       <c r="K4" s="136" t="s">
         <v>14</v>
@@ -27520,8 +27529,8 @@
         <v>118</v>
       </c>
       <c r="I4" s="150"/>
-      <c r="J4" s="133" t="s">
-        <v>13</v>
+      <c r="J4" s="130" t="s">
+        <v>311</v>
       </c>
       <c r="K4" s="136" t="s">
         <v>14</v>
@@ -27854,11 +27863,11 @@
       <c r="C17" s="130" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="133" t="s">
+      <c r="D17" s="164" t="s">
         <v>146</v>
       </c>
-      <c r="E17" s="150" t="s">
-        <v>275</v>
+      <c r="E17" s="130" t="s">
+        <v>313</v>
       </c>
       <c r="F17" s="150" t="s">
         <v>46</v>
@@ -27972,8 +27981,8 @@
       <c r="B22" s="133" t="s">
         <v>111</v>
       </c>
-      <c r="C22" s="360" t="s">
-        <v>73</v>
+      <c r="C22" s="365" t="s">
+        <v>214</v>
       </c>
       <c r="D22" s="133" t="s">
         <v>91</v>
@@ -28001,9 +28010,7 @@
       <c r="B23" s="133" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="143" t="s">
-        <v>291</v>
-      </c>
+      <c r="C23" s="139"/>
       <c r="D23" s="133" t="s">
         <v>182</v>
       </c>
@@ -28013,8 +28020,8 @@
         <v>303</v>
       </c>
       <c r="H23" s="189"/>
-      <c r="I23" s="213" t="s">
-        <v>187</v>
+      <c r="I23" s="350" t="s">
+        <v>314</v>
       </c>
       <c r="J23" s="207" t="s">
         <v>149</v>
@@ -28073,7 +28080,7 @@
       <c r="D26" s="205"/>
       <c r="E26" s="139"/>
       <c r="F26" s="139"/>
-      <c r="G26" s="159"/>
+      <c r="G26" s="150"/>
       <c r="H26" s="204"/>
       <c r="I26" s="197" t="s">
         <v>52</v>
@@ -28171,6 +28178,777 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0AB9A2A-C1F8-4E49-BA47-A17B48C68948}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="11" width="11.81640625" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.90625" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="319"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="360"/>
+      <c r="F1" s="364" t="s">
+        <v>312</v>
+      </c>
+      <c r="G1" s="364"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="320"/>
+    </row>
+    <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="137" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="323" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="137" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="140" t="s">
+        <v>241</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="130" t="s">
+        <v>311</v>
+      </c>
+      <c r="K4" s="136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="145"/>
+      <c r="B5" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="156" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="136" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="137"/>
+      <c r="B6" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="136" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="324" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="130"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="K7" s="136" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="137" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="323" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="130" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="164" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>250</v>
+      </c>
+      <c r="K9" s="325" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="137" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="235" t="s">
+        <v>259</v>
+      </c>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>208</v>
+      </c>
+      <c r="K10" s="323" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="137"/>
+      <c r="B11" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="143" t="s">
+        <v>299</v>
+      </c>
+      <c r="K11" s="323" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="169" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="143" t="s">
+        <v>300</v>
+      </c>
+      <c r="K12" s="323" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="137" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="143" t="s">
+        <v>191</v>
+      </c>
+      <c r="K13" s="326" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="137" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="263" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="141" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="327" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="177"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="359" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="120" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="234"/>
+      <c r="K16" s="329"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="182" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>315</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="K17" s="330"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="120"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="352"/>
+      <c r="H18" s="159" t="s">
+        <v>305</v>
+      </c>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="330"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="185"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="188"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="120" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="189"/>
+      <c r="I20" s="340" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="341" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="342" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="331" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="139" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="141" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="189"/>
+      <c r="I21" s="348" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="349" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="225"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="192" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>174</v>
+      </c>
+      <c r="C22" s="365" t="s">
+        <v>214</v>
+      </c>
+      <c r="D22" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="189"/>
+      <c r="I22" s="197" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="194"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="331" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" s="143" t="s">
+        <v>298</v>
+      </c>
+      <c r="C23" s="234"/>
+      <c r="D23" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="143" t="s">
+        <v>303</v>
+      </c>
+      <c r="H23" s="189"/>
+      <c r="I23" s="213" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="203"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="192" t="s">
+        <v>198</v>
+      </c>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="H24" s="156"/>
+      <c r="I24" s="197" t="s">
+        <v>309</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="194"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="358" t="s">
+        <v>200</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="157"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="189"/>
+      <c r="I25" s="197" t="s">
+        <v>186</v>
+      </c>
+      <c r="J25" s="193" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" s="203"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="358" t="s">
+        <v>199</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="205"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="204"/>
+      <c r="I26" s="197" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="355" t="s">
+        <v>308</v>
+      </c>
+      <c r="K26" s="203"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" s="201" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="287"/>
+      <c r="I27" s="350" t="s">
+        <v>181</v>
+      </c>
+      <c r="J27" s="237"/>
+      <c r="K27" s="203"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="195"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="287"/>
+      <c r="I28" s="350"/>
+      <c r="J28" s="207"/>
+      <c r="K28" s="210" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="195"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="350"/>
+      <c r="J29" s="207"/>
+      <c r="K29" s="316" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="333"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="189"/>
+      <c r="I30" s="350"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="179" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="334"/>
+      <c r="B31" s="335"/>
+      <c r="C31" s="220"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="337"/>
+      <c r="G31" s="338"/>
+      <c r="H31" s="339"/>
+      <c r="I31" s="317"/>
+      <c r="J31" s="220"/>
+      <c r="K31" s="318" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D176BE15-88C5-4E9C-A22B-97E5C8DAA045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDE5919-709C-4FC6-8CCC-3EDA76A95A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="23" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="24" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -45,6 +45,7 @@
     <sheet name="27.10 Түскі ауысым" sheetId="180" r:id="rId35"/>
     <sheet name="28.10" sheetId="181" r:id="rId36"/>
     <sheet name="29.10" sheetId="182" r:id="rId37"/>
+    <sheet name="30.10" sheetId="183" r:id="rId38"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -219,7 +220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6467" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6641" uniqueCount="317">
   <si>
     <t>СБ</t>
   </si>
@@ -1185,6 +1186,9 @@
   <si>
     <t xml:space="preserve">С12-Н798399 </t>
   </si>
+  <si>
+    <t xml:space="preserve">30.10.2026 ж </t>
+  </si>
 </sst>
 </file>
 
@@ -1886,7 +1890,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="366">
+  <cellXfs count="368">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2882,6 +2886,12 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2894,7 +2904,7 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3217,10 +3227,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="361" t="s">
+      <c r="F1" s="363" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="362"/>
+      <c r="G1" s="364"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -4269,10 +4279,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5178,10 +5188,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6098,10 +6108,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7012,10 +7022,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7938,10 +7948,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8862,10 +8872,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9781,10 +9791,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10702,10 +10712,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11622,10 +11632,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12407,10 +12417,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -13190,10 +13200,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="361" t="s">
+      <c r="F1" s="363" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="362"/>
+      <c r="G1" s="364"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -14094,10 +14104,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14872,10 +14882,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15650,10 +15660,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16426,10 +16436,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17202,10 +17212,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17978,10 +17988,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18756,10 +18766,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19533,10 +19543,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="310"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20311,10 +20321,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="311"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21091,10 +21101,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="312"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>290</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21882,10 +21892,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="361" t="s">
+      <c r="F1" s="363" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="362"/>
+      <c r="G1" s="364"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22786,10 +22796,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="313"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>295</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -23567,10 +23577,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="314"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -24345,10 +24355,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="364" t="s">
+      <c r="F1" s="366" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25114,10 +25124,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="343"/>
-      <c r="F1" s="364" t="s">
+      <c r="F1" s="366" t="s">
         <v>304</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25884,10 +25894,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="347"/>
-      <c r="F1" s="364" t="s">
+      <c r="F1" s="366" t="s">
         <v>306</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -26656,10 +26666,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="353"/>
-      <c r="F1" s="364" t="s">
+      <c r="F1" s="366" t="s">
         <v>306</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -27426,10 +27436,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="353"/>
-      <c r="F1" s="364" t="s">
+      <c r="F1" s="366" t="s">
         <v>310</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -27981,7 +27991,7 @@
       <c r="B22" s="133" t="s">
         <v>111</v>
       </c>
-      <c r="C22" s="365" t="s">
+      <c r="C22" s="362" t="s">
         <v>214</v>
       </c>
       <c r="D22" s="133" t="s">
@@ -28196,10 +28206,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="360"/>
-      <c r="F1" s="364" t="s">
+      <c r="F1" s="366" t="s">
         <v>312</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -28754,7 +28764,7 @@
       <c r="B22" s="133" t="s">
         <v>174</v>
       </c>
-      <c r="C22" s="365" t="s">
+      <c r="C22" s="362" t="s">
         <v>214</v>
       </c>
       <c r="D22" s="133" t="s">
@@ -28855,9 +28865,780 @@
       <c r="I26" s="197" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="355" t="s">
+      <c r="J26" s="207" t="s">
         <v>308</v>
       </c>
+      <c r="K26" s="203"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" s="201" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="287"/>
+      <c r="I27" s="350" t="s">
+        <v>181</v>
+      </c>
+      <c r="J27" s="237"/>
+      <c r="K27" s="203"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="195"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="287"/>
+      <c r="I28" s="350"/>
+      <c r="J28" s="207"/>
+      <c r="K28" s="210" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="195"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="350"/>
+      <c r="J29" s="207"/>
+      <c r="K29" s="316" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="333"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="189"/>
+      <c r="I30" s="350"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="179" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="334"/>
+      <c r="B31" s="335"/>
+      <c r="C31" s="220"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="337"/>
+      <c r="G31" s="338"/>
+      <c r="H31" s="339"/>
+      <c r="I31" s="317"/>
+      <c r="J31" s="220"/>
+      <c r="K31" s="318" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651E8DBF-0EA5-4163-A054-C03BBCA27337}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="11" width="11.81640625" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.90625" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="319"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="361"/>
+      <c r="F1" s="366" t="s">
+        <v>316</v>
+      </c>
+      <c r="G1" s="366"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="320"/>
+    </row>
+    <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="137" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="323" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="137" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="140" t="s">
+        <v>241</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="130" t="s">
+        <v>311</v>
+      </c>
+      <c r="K4" s="136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="145"/>
+      <c r="B5" s="130" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="156" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="136" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="137"/>
+      <c r="B6" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="136" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="324" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="130"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="K7" s="136" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="137" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="323" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="130" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="164" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>250</v>
+      </c>
+      <c r="K9" s="325" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="137" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="235" t="s">
+        <v>259</v>
+      </c>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>208</v>
+      </c>
+      <c r="K10" s="323" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="137"/>
+      <c r="B11" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="143" t="s">
+        <v>299</v>
+      </c>
+      <c r="K11" s="323" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="169" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="143" t="s">
+        <v>300</v>
+      </c>
+      <c r="K12" s="323" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="137" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="143" t="s">
+        <v>191</v>
+      </c>
+      <c r="K13" s="326" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="137" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="263" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="141" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="327" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="177"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="359" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="120" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="234"/>
+      <c r="K16" s="329"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="182" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>315</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="K17" s="330"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="120"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="352"/>
+      <c r="H18" s="159" t="s">
+        <v>305</v>
+      </c>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="330"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="185"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="188"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="120" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="189"/>
+      <c r="I20" s="340" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="341" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="342" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="331" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="139" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="141" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="189"/>
+      <c r="I21" s="348" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="349" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="225"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="192" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>174</v>
+      </c>
+      <c r="C22" s="367" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="189"/>
+      <c r="I22" s="197" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="194"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="331" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" s="143" t="s">
+        <v>298</v>
+      </c>
+      <c r="C23" s="143" t="s">
+        <v>291</v>
+      </c>
+      <c r="D23" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="143" t="s">
+        <v>303</v>
+      </c>
+      <c r="H23" s="189"/>
+      <c r="I23" s="213" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="203"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="192" t="s">
+        <v>198</v>
+      </c>
+      <c r="C24" s="234"/>
+      <c r="D24" s="267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="H24" s="156"/>
+      <c r="I24" s="197" t="s">
+        <v>309</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="194"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="358" t="s">
+        <v>200</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="157"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="189"/>
+      <c r="I25" s="197" t="s">
+        <v>186</v>
+      </c>
+      <c r="J25" s="193" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" s="203"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="358" t="s">
+        <v>199</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="205"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="204"/>
+      <c r="I26" s="197" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="207"/>
       <c r="K26" s="203"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -28977,10 +29758,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="361" t="s">
+      <c r="F1" s="363" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="362"/>
+      <c r="G1" s="364"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -29891,10 +30672,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="361" t="s">
+      <c r="F1" s="363" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="362"/>
+      <c r="G1" s="364"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -30807,10 +31588,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="361" t="s">
+      <c r="F1" s="363" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="362"/>
+      <c r="G1" s="364"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -31725,10 +32506,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -32643,10 +33424,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -33556,10 +34337,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="363"/>
+      <c r="G1" s="365"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDE5919-709C-4FC6-8CCC-3EDA76A95A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8E79BA-393C-402A-BED2-2E05EA7BB71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="24" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="25" activeTab="38" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -46,6 +46,7 @@
     <sheet name="28.10" sheetId="181" r:id="rId36"/>
     <sheet name="29.10" sheetId="182" r:id="rId37"/>
     <sheet name="30.10" sheetId="183" r:id="rId38"/>
+    <sheet name="31.10" sheetId="184" r:id="rId39"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -220,7 +221,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6641" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6817" uniqueCount="318">
   <si>
     <t>СБ</t>
   </si>
@@ -1189,6 +1190,9 @@
   <si>
     <t xml:space="preserve">30.10.2026 ж </t>
   </si>
+  <si>
+    <t xml:space="preserve">31.10.2026 ж </t>
+  </si>
 </sst>
 </file>
 
@@ -1890,7 +1894,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2892,6 +2896,12 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2904,7 +2914,7 @@
     <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="3" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2922,8 +2932,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0F0FF9"/>
       <color rgb="FF660033"/>
-      <color rgb="FF0F0FF9"/>
       <color rgb="FFFF99FF"/>
       <color rgb="FFFF66FF"/>
       <color rgb="FFFF00FF"/>
@@ -3227,10 +3237,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -4279,10 +4289,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5188,10 +5198,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6108,10 +6118,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7022,10 +7032,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7948,10 +7958,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8872,10 +8882,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9791,10 +9801,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10712,10 +10722,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11632,10 +11642,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12417,10 +12427,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -13200,10 +13210,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -14104,10 +14114,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14882,10 +14892,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15660,10 +15670,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16436,10 +16446,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17212,10 +17222,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17988,10 +17998,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18766,10 +18776,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19543,10 +19553,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="310"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20321,10 +20331,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="311"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21101,10 +21111,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="312"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>290</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21892,10 +21902,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22796,10 +22806,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="313"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>295</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -23577,10 +23587,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="314"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -24355,10 +24365,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="366" t="s">
+      <c r="F1" s="368" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25124,10 +25134,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="343"/>
-      <c r="F1" s="366" t="s">
+      <c r="F1" s="368" t="s">
         <v>304</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25894,10 +25904,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="347"/>
-      <c r="F1" s="366" t="s">
+      <c r="F1" s="368" t="s">
         <v>306</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -26666,10 +26676,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="353"/>
-      <c r="F1" s="366" t="s">
+      <c r="F1" s="368" t="s">
         <v>306</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -27436,10 +27446,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="353"/>
-      <c r="F1" s="366" t="s">
+      <c r="F1" s="368" t="s">
         <v>310</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -28206,10 +28216,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="360"/>
-      <c r="F1" s="366" t="s">
+      <c r="F1" s="368" t="s">
         <v>312</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -28977,10 +28987,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="361"/>
-      <c r="F1" s="366" t="s">
+      <c r="F1" s="368" t="s">
         <v>316</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -29535,7 +29545,7 @@
       <c r="B22" s="133" t="s">
         <v>174</v>
       </c>
-      <c r="C22" s="367" t="s">
+      <c r="C22" s="364" t="s">
         <v>73</v>
       </c>
       <c r="D22" s="133" t="s">
@@ -29564,8 +29574,8 @@
       <c r="B23" s="143" t="s">
         <v>298</v>
       </c>
-      <c r="C23" s="143" t="s">
-        <v>291</v>
+      <c r="C23" s="141" t="s">
+        <v>280</v>
       </c>
       <c r="D23" s="133" t="s">
         <v>182</v>
@@ -29588,7 +29598,9 @@
       <c r="A24" s="192" t="s">
         <v>198</v>
       </c>
-      <c r="C24" s="234"/>
+      <c r="C24" s="143" t="s">
+        <v>291</v>
+      </c>
       <c r="D24" s="267" t="s">
         <v>178</v>
       </c>
@@ -29730,6 +29742,778 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E8A2644-F8E9-4F7E-BAA9-2AE2F7585BF2}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="11" width="11.81640625" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.90625" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="319"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="363"/>
+      <c r="F1" s="368" t="s">
+        <v>317</v>
+      </c>
+      <c r="G1" s="368"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="320"/>
+    </row>
+    <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="137" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="323" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="137" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="133" t="s">
+        <v>241</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="130" t="s">
+        <v>311</v>
+      </c>
+      <c r="K4" s="136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="145"/>
+      <c r="B5" s="156" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="159" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="136" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="137"/>
+      <c r="B6" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="156" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="136" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="324" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="130"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>120</v>
+      </c>
+      <c r="K7" s="136" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="137" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="323" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="130" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="164" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>250</v>
+      </c>
+      <c r="K9" s="325" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="137" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="141"/>
+      <c r="H10" s="235" t="s">
+        <v>259</v>
+      </c>
+      <c r="I10" s="133"/>
+      <c r="J10" s="133" t="s">
+        <v>208</v>
+      </c>
+      <c r="K10" s="323" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="137"/>
+      <c r="B11" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="143" t="s">
+        <v>299</v>
+      </c>
+      <c r="K11" s="323" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="169" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="143" t="s">
+        <v>300</v>
+      </c>
+      <c r="K12" s="323" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="137" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="143" t="s">
+        <v>191</v>
+      </c>
+      <c r="K13" s="326" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="137" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="263" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="141" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="327" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="177"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="369" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="120" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="234"/>
+      <c r="K16" s="329"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="182" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>315</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="K17" s="330"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="120"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="352"/>
+      <c r="H18" s="159" t="s">
+        <v>305</v>
+      </c>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="330"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="185"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="188"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="120" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="189"/>
+      <c r="I20" s="340" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="341" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="342" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="331" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="139" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="141" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" s="189"/>
+      <c r="I21" s="348" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="349" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="225"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="192" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>174</v>
+      </c>
+      <c r="C22" s="364" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="133" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="189"/>
+      <c r="I22" s="197" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="194"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="331" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" s="143" t="s">
+        <v>298</v>
+      </c>
+      <c r="C23" s="141" t="s">
+        <v>280</v>
+      </c>
+      <c r="D23" s="133" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="143" t="s">
+        <v>303</v>
+      </c>
+      <c r="H23" s="189"/>
+      <c r="I23" s="213" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" s="203"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="192" t="s">
+        <v>198</v>
+      </c>
+      <c r="C24" s="143" t="s">
+        <v>291</v>
+      </c>
+      <c r="D24" s="267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="H24" s="156"/>
+      <c r="I24" s="197" t="s">
+        <v>309</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K24" s="194"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="358" t="s">
+        <v>200</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="157"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="189"/>
+      <c r="I25" s="197" t="s">
+        <v>186</v>
+      </c>
+      <c r="J25" s="193" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" s="203"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="358" t="s">
+        <v>199</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="205"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="204"/>
+      <c r="I26" s="197" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="207"/>
+      <c r="K26" s="203"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" s="201" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="287"/>
+      <c r="I27" s="350" t="s">
+        <v>181</v>
+      </c>
+      <c r="J27" s="237"/>
+      <c r="K27" s="203"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="195"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="287"/>
+      <c r="I28" s="350"/>
+      <c r="J28" s="207"/>
+      <c r="K28" s="210" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="195"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="350"/>
+      <c r="J29" s="207"/>
+      <c r="K29" s="316" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="333"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="189"/>
+      <c r="I30" s="350"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="179" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="334"/>
+      <c r="B31" s="335"/>
+      <c r="C31" s="220"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="337"/>
+      <c r="G31" s="338"/>
+      <c r="H31" s="339"/>
+      <c r="I31" s="317"/>
+      <c r="J31" s="220"/>
+      <c r="K31" s="318" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -29758,10 +30542,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -30672,10 +31456,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -31588,10 +32372,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="363" t="s">
+      <c r="F1" s="365" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="364"/>
+      <c r="G1" s="366"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -32506,10 +33290,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -33424,10 +34208,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -34337,10 +35121,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="365"/>
+      <c r="G1" s="367"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>

--- a/raw/SB.xlsx
+++ b/raw/SB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8E79BA-393C-402A-BED2-2E05EA7BB71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E223C9E8-967F-4237-9D38-F89C56975A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="25" activeTab="38" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" firstSheet="27" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="30" sheetId="145" r:id="rId1"/>
@@ -47,6 +47,7 @@
     <sheet name="29.10" sheetId="182" r:id="rId37"/>
     <sheet name="30.10" sheetId="183" r:id="rId38"/>
     <sheet name="31.10" sheetId="184" r:id="rId39"/>
+    <sheet name="31.10 түскі ауысым" sheetId="185" r:id="rId40"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -221,7 +222,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6817" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6991" uniqueCount="320">
   <si>
     <t>СБ</t>
   </si>
@@ -1193,6 +1194,12 @@
   <si>
     <t xml:space="preserve">31.10.2026 ж </t>
   </si>
+  <si>
+    <t>34-Н2892/12н</t>
+  </si>
+  <si>
+    <t>34-Н2861/12д/н</t>
+  </si>
 </sst>
 </file>
 
@@ -1894,7 +1901,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="371">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2902,6 +2909,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="6" fillId="3" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2912,9 +2925,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="3" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2932,8 +2942,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF660033"/>
       <color rgb="FF0F0FF9"/>
-      <color rgb="FF660033"/>
       <color rgb="FFFF99FF"/>
       <color rgb="FFFF66FF"/>
       <color rgb="FFFF00FF"/>
@@ -3237,10 +3247,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>169</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -4289,10 +4299,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="265"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -5198,10 +5208,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -6118,10 +6128,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="271"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>228</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7032,10 +7042,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="272"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -7958,10 +7968,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="279"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>240</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -8882,10 +8892,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="280"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -9801,10 +9811,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="266"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -10722,10 +10732,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="285"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>246</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="290"/>
@@ -11642,10 +11652,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="295"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -12427,10 +12437,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="297"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -13210,10 +13220,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>168</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -14114,10 +14124,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="298"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>260</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -14892,10 +14902,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="301"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -15670,10 +15680,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="302"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>263</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -16446,10 +16456,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="304"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17222,10 +17232,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="305"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -17998,10 +18008,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="307"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -18776,10 +18786,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="309"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>286</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -19553,10 +19563,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="310"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -20331,10 +20341,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="311"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>287</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21111,10 +21121,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="312"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>290</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -21902,10 +21912,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -22806,10 +22816,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="313"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>295</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -23587,10 +23597,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="314"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -24365,10 +24375,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="368" t="s">
+      <c r="F1" s="370" t="s">
         <v>297</v>
       </c>
-      <c r="G1" s="368"/>
+      <c r="G1" s="370"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25134,10 +25144,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="343"/>
-      <c r="F1" s="368" t="s">
+      <c r="F1" s="370" t="s">
         <v>304</v>
       </c>
-      <c r="G1" s="368"/>
+      <c r="G1" s="370"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -25904,10 +25914,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="347"/>
-      <c r="F1" s="368" t="s">
+      <c r="F1" s="370" t="s">
         <v>306</v>
       </c>
-      <c r="G1" s="368"/>
+      <c r="G1" s="370"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -26676,10 +26686,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="353"/>
-      <c r="F1" s="368" t="s">
+      <c r="F1" s="370" t="s">
         <v>306</v>
       </c>
-      <c r="G1" s="368"/>
+      <c r="G1" s="370"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -27446,10 +27456,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="353"/>
-      <c r="F1" s="368" t="s">
+      <c r="F1" s="370" t="s">
         <v>310</v>
       </c>
-      <c r="G1" s="368"/>
+      <c r="G1" s="370"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -28216,10 +28226,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="360"/>
-      <c r="F1" s="368" t="s">
+      <c r="F1" s="370" t="s">
         <v>312</v>
       </c>
-      <c r="G1" s="368"/>
+      <c r="G1" s="370"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -28987,10 +28997,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="361"/>
-      <c r="F1" s="368" t="s">
+      <c r="F1" s="370" t="s">
         <v>316</v>
       </c>
-      <c r="G1" s="368"/>
+      <c r="G1" s="370"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -29267,9 +29277,7 @@
       <c r="F10" s="133" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="141" t="s">
-        <v>280</v>
-      </c>
+      <c r="G10" s="141"/>
       <c r="H10" s="235" t="s">
         <v>259</v>
       </c>
@@ -29760,10 +29768,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="363"/>
-      <c r="F1" s="368" t="s">
+      <c r="F1" s="370" t="s">
         <v>317</v>
       </c>
-      <c r="G1" s="368"/>
+      <c r="G1" s="370"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -30150,7 +30158,7 @@
       <c r="J15" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="K15" s="369" t="s">
+      <c r="K15" s="365" t="s">
         <v>63</v>
       </c>
     </row>
@@ -30333,8 +30341,8 @@
       <c r="I22" s="197" t="s">
         <v>163</v>
       </c>
-      <c r="J22" s="207" t="s">
-        <v>141</v>
+      <c r="J22" s="351" t="s">
+        <v>25</v>
       </c>
       <c r="K22" s="194"/>
     </row>
@@ -30361,7 +30369,7 @@
         <v>187</v>
       </c>
       <c r="J23" s="207" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="K23" s="203"/>
     </row>
@@ -30382,7 +30390,7 @@
         <v>309</v>
       </c>
       <c r="J24" s="207" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="K24" s="194"/>
     </row>
@@ -30400,8 +30408,8 @@
       <c r="I25" s="197" t="s">
         <v>186</v>
       </c>
-      <c r="J25" s="193" t="s">
-        <v>56</v>
+      <c r="J25" s="207" t="s">
+        <v>159</v>
       </c>
       <c r="K25" s="203"/>
     </row>
@@ -30416,14 +30424,14 @@
       <c r="D26" s="205"/>
       <c r="E26" s="139"/>
       <c r="F26" s="139"/>
-      <c r="G26" s="130" t="s">
-        <v>25</v>
-      </c>
+      <c r="G26" s="130"/>
       <c r="H26" s="204"/>
       <c r="I26" s="197" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="207"/>
+      <c r="J26" s="193" t="s">
+        <v>56</v>
+      </c>
       <c r="K26" s="203"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -30542,10 +30550,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>192</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -31428,6 +31436,776 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06FD0D34-62E9-4B7F-86E1-1A082385E15D}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr defaultColWidth="13.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="11" width="11.81640625" style="122" customWidth="1"/>
+    <col min="12" max="16384" width="13.90625" style="122"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="319"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="366"/>
+      <c r="F1" s="370" t="s">
+        <v>317</v>
+      </c>
+      <c r="G1" s="370"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="320"/>
+    </row>
+    <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="321" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="137" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="130" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" s="133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="130" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="267" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="323" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="137" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="130" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="141"/>
+      <c r="G4" s="133" t="s">
+        <v>241</v>
+      </c>
+      <c r="H4" s="141" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="150"/>
+      <c r="J4" s="130" t="s">
+        <v>311</v>
+      </c>
+      <c r="K4" s="136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="145"/>
+      <c r="B5" s="156" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="159" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="130" t="s">
+        <v>203</v>
+      </c>
+      <c r="E5" s="138"/>
+      <c r="F5" s="160"/>
+      <c r="G5" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="141" t="s">
+        <v>119</v>
+      </c>
+      <c r="I5" s="140"/>
+      <c r="J5" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="136" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="137"/>
+      <c r="B6" s="224" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="156" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="130" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="133" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="141" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="136" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="324" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="130" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="130" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="130"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>110</v>
+      </c>
+      <c r="K7" s="136" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="137" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="130" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="151" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="159"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="141" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="323" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="299"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="130" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="130" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="162" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="133" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>208</v>
+      </c>
+      <c r="K9" s="325" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="300"/>
+    </row>
+    <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="137" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="267" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="151" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="133" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="141"/>
+      <c r="H10" s="291" t="s">
+        <v>172</v>
+      </c>
+      <c r="I10" s="133"/>
+      <c r="J10" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="K10" s="323" t="s">
+        <v>109</v>
+      </c>
+      <c r="L10" s="283"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="137"/>
+      <c r="B11" s="130" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="249"/>
+      <c r="D11" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="143" t="s">
+        <v>299</v>
+      </c>
+      <c r="K11" s="323" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="169" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="234"/>
+      <c r="D12" s="267" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="234"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="235" t="s">
+        <v>232</v>
+      </c>
+      <c r="K12" s="323" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="137" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="170" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" s="178"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="141" t="s">
+        <v>55</v>
+      </c>
+      <c r="K13" s="326" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="137" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="263" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="157"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="160"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="133" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="327" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="177"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="245"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="166"/>
+      <c r="I15" s="140"/>
+      <c r="K15" s="365" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="120" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="180" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="162" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="181" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="166" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="234"/>
+      <c r="K16" s="329"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="182" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="133" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="150" t="s">
+        <v>315</v>
+      </c>
+      <c r="F17" s="150" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="K17" s="330"/>
+    </row>
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="120"/>
+      <c r="B18" s="157"/>
+      <c r="C18" s="140"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="150" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="352"/>
+      <c r="H18" s="159" t="s">
+        <v>305</v>
+      </c>
+      <c r="I18" s="157"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="330"/>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="185"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="160"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="166"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="188"/>
+    </row>
+    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="120" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="162" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="121" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="189"/>
+      <c r="I20" s="340" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="341" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="342" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="331" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="133" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="133" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="139" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="141" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="267" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="139" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="189"/>
+      <c r="I21" s="348" t="s">
+        <v>112</v>
+      </c>
+      <c r="J21" s="349" t="s">
+        <v>201</v>
+      </c>
+      <c r="K21" s="225"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="192" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="139" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" s="364" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="160"/>
+      <c r="F22" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="139" t="s">
+        <v>164</v>
+      </c>
+      <c r="H22" s="189"/>
+      <c r="I22" s="197" t="s">
+        <v>163</v>
+      </c>
+      <c r="J22" s="351" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" s="194"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="331" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" s="143" t="s">
+        <v>318</v>
+      </c>
+      <c r="C23" s="143" t="s">
+        <v>291</v>
+      </c>
+      <c r="D23" s="139" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" s="165"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="143" t="s">
+        <v>251</v>
+      </c>
+      <c r="H23" s="189"/>
+      <c r="I23" s="213" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" s="207" t="s">
+        <v>141</v>
+      </c>
+      <c r="K23" s="203"/>
+    </row>
+    <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="192" t="s">
+        <v>198</v>
+      </c>
+      <c r="C24" s="143" t="s">
+        <v>285</v>
+      </c>
+      <c r="D24" s="143" t="s">
+        <v>166</v>
+      </c>
+      <c r="E24" s="234"/>
+      <c r="F24" s="234"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="156"/>
+      <c r="I24" s="197" t="s">
+        <v>309</v>
+      </c>
+      <c r="J24" s="207" t="s">
+        <v>149</v>
+      </c>
+      <c r="K24" s="194"/>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="358" t="s">
+        <v>200</v>
+      </c>
+      <c r="B25" s="234"/>
+      <c r="D25" s="205"/>
+      <c r="E25" s="157"/>
+      <c r="F25" s="157"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="189"/>
+      <c r="I25" s="197" t="s">
+        <v>186</v>
+      </c>
+      <c r="J25" s="207" t="s">
+        <v>159</v>
+      </c>
+      <c r="K25" s="203"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="358" t="s">
+        <v>199</v>
+      </c>
+      <c r="B26" s="234"/>
+      <c r="C26" s="133" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="205"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="204"/>
+      <c r="I26" s="197" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="193" t="s">
+        <v>56</v>
+      </c>
+      <c r="K26" s="203"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" s="201" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="205"/>
+      <c r="C27" s="207"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="133"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="287"/>
+      <c r="I27" s="350" t="s">
+        <v>181</v>
+      </c>
+      <c r="J27" s="351" t="s">
+        <v>120</v>
+      </c>
+      <c r="K27" s="203"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="195"/>
+      <c r="B28" s="157"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="287"/>
+      <c r="I28" s="350"/>
+      <c r="J28" s="207"/>
+      <c r="K28" s="210" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="195"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="209" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="157"/>
+      <c r="H29" s="189"/>
+      <c r="I29" s="350"/>
+      <c r="J29" s="207"/>
+      <c r="K29" s="316" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="333"/>
+      <c r="B30" s="157"/>
+      <c r="C30" s="207"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="166"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="244"/>
+      <c r="H30" s="189"/>
+      <c r="I30" s="350"/>
+      <c r="J30" s="207"/>
+      <c r="K30" s="179" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="334"/>
+      <c r="B31" s="335"/>
+      <c r="C31" s="220"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="337"/>
+      <c r="G31" s="338"/>
+      <c r="H31" s="339"/>
+      <c r="I31" s="317"/>
+      <c r="J31" s="220"/>
+      <c r="K31" s="318" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D32" s="123"/>
+      <c r="H32" s="123"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -31456,10 +32234,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -32372,10 +33150,10 @@
       <c r="C1" s="118"/>
       <c r="D1" s="119"/>
       <c r="E1" s="124"/>
-      <c r="F1" s="365" t="s">
+      <c r="F1" s="367" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="366"/>
+      <c r="G1" s="368"/>
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
       <c r="J1" s="117"/>
@@ -33290,10 +34068,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="246"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -34208,10 +34986,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="254"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
@@ -35121,10 +35899,10 @@
       <c r="C1" s="243"/>
       <c r="D1" s="245"/>
       <c r="E1" s="260"/>
-      <c r="F1" s="367" t="s">
+      <c r="F1" s="369" t="s">
         <v>221</v>
       </c>
-      <c r="G1" s="367"/>
+      <c r="G1" s="369"/>
       <c r="H1" s="244"/>
       <c r="I1" s="244"/>
       <c r="J1" s="244"/>
